--- a/data/exports/MFAS_Data_Warehouse.xlsx
+++ b/data/exports/MFAS_Data_Warehouse.xlsx
@@ -856,7 +856,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FY2012</t>
+          <t>FY12</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -879,7 +879,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FY2013</t>
+          <t>FY13</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -917,7 +917,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FY2014</t>
+          <t>FY14</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -955,7 +955,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FY2015</t>
+          <t>FY15</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -993,7 +993,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FY2016</t>
+          <t>FY16</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1031,7 +1031,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FY2017</t>
+          <t>FY17</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1069,7 +1069,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FY2018</t>
+          <t>FY18</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1104,7 +1104,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FY2019</t>
+          <t>FY19</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1139,7 +1139,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FY2020</t>
+          <t>FY20</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1174,7 +1174,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FY2021</t>
+          <t>FY21</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1206,7 +1206,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FY2022</t>
+          <t>FY22</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1244,7 +1244,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY23</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1282,7 +1282,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY24</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1320,7 +1320,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1358,7 +1358,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FY2026</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1390,7 +1390,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1498,7 +1498,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FY2018</t>
+          <t>FY18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1533,7 +1533,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FY2019</t>
+          <t>FY19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1568,7 +1568,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FY2019</t>
+          <t>FY19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FY2019</t>
+          <t>FY19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1638,7 +1638,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FY2019</t>
+          <t>FY19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1673,7 +1673,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FY2019</t>
+          <t>FY19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1708,7 +1708,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FY2019</t>
+          <t>FY19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1743,7 +1743,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FY2020</t>
+          <t>FY20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1778,7 +1778,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FY2020</t>
+          <t>FY20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1813,7 +1813,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FY2020</t>
+          <t>FY20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1848,7 +1848,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FY2020</t>
+          <t>FY20</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1883,7 +1883,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FY2020</t>
+          <t>FY20</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1918,7 +1918,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FY2020</t>
+          <t>FY20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1953,7 +1953,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FY2021</t>
+          <t>FY21</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1988,7 +1988,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FY2021</t>
+          <t>FY21</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2023,7 +2023,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FY2021</t>
+          <t>FY21</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2058,7 +2058,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FY2021</t>
+          <t>FY21</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2093,7 +2093,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FY2021</t>
+          <t>FY21</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2128,7 +2128,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FY2021</t>
+          <t>FY21</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2163,7 +2163,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FY2022</t>
+          <t>FY22</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2198,7 +2198,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FY2022</t>
+          <t>FY22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2233,7 +2233,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FY2022</t>
+          <t>FY22</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2268,7 +2268,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FY2022</t>
+          <t>FY22</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2303,7 +2303,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FY2022</t>
+          <t>FY22</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2338,7 +2338,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FY2022</t>
+          <t>FY22</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2373,7 +2373,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY23</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2408,7 +2408,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY23</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2443,7 +2443,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY23</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2478,7 +2478,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY23</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY23</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2548,7 +2548,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY23</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2583,7 +2583,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY24</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2618,7 +2618,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY24</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2653,7 +2653,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY24</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2688,7 +2688,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2723,7 +2723,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY24</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2758,7 +2758,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY24</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2793,7 +2793,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY24</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2828,7 +2828,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2863,7 +2863,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2898,7 +2898,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2933,7 +2933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2968,7 +2968,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3003,7 +3003,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3038,7 +3038,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3073,7 +3073,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FY2026</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3111,7 +3111,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>FY2026</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3149,7 +3149,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>FY2026</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3187,7 +3187,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FY2026</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3225,7 +3225,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>FY2026</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3263,7 +3263,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FY2026</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3301,7 +3301,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FY2026</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3339,7 +3339,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FY2026</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3377,7 +3377,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3415,7 +3415,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3453,7 +3453,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3491,7 +3491,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3529,7 +3529,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3567,7 +3567,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3605,7 +3605,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3643,7 +3643,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3697,7 +3697,7 @@
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="42" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Entity_ID</t>
+          <t>Organization_ID</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -8205,7 +8205,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FY2026</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -8246,7 +8246,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -8287,7 +8287,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FY2026</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -8328,7 +8328,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -8369,7 +8369,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FY2026</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -8410,7 +8410,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -8451,7 +8451,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FY2026</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -8492,7 +8492,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -11980,7 +11980,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Everything the project publishes, in one place, in the schema of your Orange_County_Municipal_Financial_Information_System_v2.2_Foundation.</t>
+          <t>Everything the project publishes, in one place, in the schema of your Hillsborough_Municipal_Financial_Database — Organization_ID, FY## keys, Source_ID + Source_Detail. CORRECTED 2026-07-28: the first version of this export followed your Orange County v2.2 workbook instead, which was the wrong one to copy for town data.</t>
         </is>
       </c>
     </row>
@@ -11992,7 +11992,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Every Fact tab ends with Source_ID and Confidence. Fiscal_Year_ID is FY####. Entity_ID separates the two governments: ORG_HILLSBOROUGH and your ORG_OC.</t>
+          <t>Every Fact tab ends with Source_ID and Confidence. Fiscal_Year_ID is FY####. Organization_ID separates the two governments: ORG_HB and ORG_OC — your own IDs.</t>
         </is>
       </c>
     </row>
@@ -12135,7 +12135,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="42" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -12160,7 +12160,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Entity_ID</t>
+          <t>Organization_ID</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -12428,7 +12428,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FY2018</t>
+          <t>FY18</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -12561,7 +12561,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FY2018</t>
+          <t>FY18</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -12608,7 +12608,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>FY2026</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -12655,7 +12655,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -12702,7 +12702,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>FY2026</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -12796,7 +12796,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>FY2026</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -12843,7 +12843,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FY2026</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -12933,7 +12933,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -12980,7 +12980,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -13027,7 +13027,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>FY2026</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -13927,7 +13927,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -13937,7 +13937,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>FY2018</t>
+          <t>FY18</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -13974,7 +13974,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -13984,7 +13984,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>FY2018</t>
+          <t>FY18</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -14021,7 +14021,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -14031,7 +14031,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>FY2019</t>
+          <t>FY19</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -14068,7 +14068,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -14078,7 +14078,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>FY2020</t>
+          <t>FY20</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -14115,7 +14115,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -14125,7 +14125,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>FY2021</t>
+          <t>FY21</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -14162,7 +14162,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -14172,7 +14172,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>FY2022</t>
+          <t>FY22</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -14209,7 +14209,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -14219,7 +14219,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY23</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -14256,7 +14256,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -14266,7 +14266,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY24</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -14303,7 +14303,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -14313,7 +14313,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -14350,7 +14350,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -14360,7 +14360,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>FY2018</t>
+          <t>FY18</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -14397,7 +14397,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -14440,7 +14440,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -14479,7 +14479,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -14518,7 +14518,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -14561,7 +14561,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -14571,7 +14571,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>FY2026</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -14608,7 +14608,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -14618,7 +14618,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>FY2026</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -14655,7 +14655,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>FY2026</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -14702,7 +14702,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -14712,7 +14712,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>FY2026</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -14749,7 +14749,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -14759,7 +14759,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -14796,7 +14796,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -14806,7 +14806,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -14843,7 +14843,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -14853,7 +14853,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY24</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -14890,7 +14890,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -14900,7 +14900,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -14947,7 +14947,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -14984,7 +14984,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -15031,7 +15031,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -15070,7 +15070,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -15109,7 +15109,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -15152,7 +15152,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -15191,7 +15191,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -15234,7 +15234,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -15273,7 +15273,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -15316,7 +15316,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -15359,7 +15359,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -15398,7 +15398,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -15441,7 +15441,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -15494,7 +15494,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
     <col width="42" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="42" customWidth="1" min="5" max="5"/>
@@ -15535,7 +15535,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Entity_ID</t>
+          <t>Organization_ID</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -15545,12 +15545,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ORG_OC is Orange County, as in your workbook</t>
+          <t>Matches your Hillsborough database. ORG_OC is Orange County.</t>
         </is>
       </c>
     </row>
@@ -15572,7 +15572,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -15757,10 +15757,10 @@
   <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="42" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -15794,7 +15794,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -15810,7 +15810,7 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Municipal government</t>
+          <t>Primary organization</t>
         </is>
       </c>
     </row>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -15882,7 +15882,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -15909,7 +15909,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -16006,12 +16006,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FY2012</t>
+          <t>FY12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FY2012</t>
+          <t>FY12</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -16046,12 +16046,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FY2013</t>
+          <t>FY13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FY2013</t>
+          <t>FY13</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -16086,12 +16086,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FY2014</t>
+          <t>FY14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FY2014</t>
+          <t>FY14</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -16126,12 +16126,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FY2015</t>
+          <t>FY15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FY2015</t>
+          <t>FY15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -16166,12 +16166,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FY2016</t>
+          <t>FY16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FY2016</t>
+          <t>FY16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -16206,12 +16206,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FY2017</t>
+          <t>FY17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FY2017</t>
+          <t>FY17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -16246,12 +16246,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FY2018</t>
+          <t>FY18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FY2018</t>
+          <t>FY18</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -16290,12 +16290,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FY2019</t>
+          <t>FY19</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FY2019</t>
+          <t>FY19</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -16330,12 +16330,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FY2020</t>
+          <t>FY20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FY2020</t>
+          <t>FY20</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -16370,12 +16370,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FY2021</t>
+          <t>FY21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FY2021</t>
+          <t>FY21</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -16410,12 +16410,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FY2022</t>
+          <t>FY22</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>FY2022</t>
+          <t>FY22</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -16450,12 +16450,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY23</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -16490,12 +16490,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY24</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -16530,12 +16530,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -16574,12 +16574,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FY2026</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FY2026</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -16618,12 +16618,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -16658,12 +16658,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FY2028</t>
+          <t>FY28</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FY2028</t>
+          <t>FY28</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -16698,12 +16698,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FY2029</t>
+          <t>FY29</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FY2029</t>
+          <t>FY29</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -17859,7 +17859,7 @@
   <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="42" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -17881,7 +17881,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Entity_ID</t>
+          <t>Organization_ID</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -17933,12 +17933,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -17978,12 +17978,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY24</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -18023,12 +18023,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -18068,12 +18068,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FY2026</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -18113,12 +18113,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -18158,12 +18158,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -18203,12 +18203,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -18248,12 +18248,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FY2026</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -18293,12 +18293,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -18338,12 +18338,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -18383,7 +18383,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -18424,7 +18424,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -18465,7 +18465,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -18506,7 +18506,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -18547,12 +18547,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FY2026</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -18595,12 +18595,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -18643,12 +18643,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FY2028</t>
+          <t>FY28</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -18691,12 +18691,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FY2029</t>
+          <t>FY29</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -18739,12 +18739,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FY2026</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -18787,12 +18787,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -18835,12 +18835,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FY2028</t>
+          <t>FY28</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -18883,12 +18883,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FY2029</t>
+          <t>FY29</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -18931,12 +18931,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FY2026</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -18979,12 +18979,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -19027,12 +19027,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FY2028</t>
+          <t>FY28</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -19075,12 +19075,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FY2029</t>
+          <t>FY29</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -19123,12 +19123,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FY2026</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -19171,12 +19171,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -19219,12 +19219,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FY2028</t>
+          <t>FY28</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -19267,12 +19267,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FY2029</t>
+          <t>FY29</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -19315,12 +19315,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -19363,12 +19363,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FY2026</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -19411,12 +19411,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -19459,12 +19459,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FY2028</t>
+          <t>FY28</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -19507,12 +19507,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -19555,12 +19555,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FY2026</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -19603,12 +19603,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -19651,12 +19651,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FY2028</t>
+          <t>FY28</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -19699,12 +19699,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -19747,12 +19747,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>FY2026</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -19795,12 +19795,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -19843,12 +19843,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>FY2028</t>
+          <t>FY28</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -19891,12 +19891,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -19939,12 +19939,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FY2026</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -19987,12 +19987,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -20035,12 +20035,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FY2028</t>
+          <t>FY28</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -20083,12 +20083,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -20131,12 +20131,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -20179,12 +20179,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -20227,12 +20227,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -20275,12 +20275,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -20323,12 +20323,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -20371,12 +20371,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -20419,12 +20419,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>FY2029</t>
+          <t>FY29</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -20467,12 +20467,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -20515,12 +20515,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -20563,12 +20563,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>FY2026</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -20611,12 +20611,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>FY2026</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -20659,12 +20659,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -20707,12 +20707,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -20755,12 +20755,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -20803,12 +20803,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -20851,12 +20851,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -20899,12 +20899,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -20947,12 +20947,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -20995,12 +20995,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -21043,12 +21043,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -21091,12 +21091,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -21139,12 +21139,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -21187,12 +21187,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -21235,12 +21235,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -21283,12 +21283,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -21331,12 +21331,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -21379,12 +21379,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -21427,12 +21427,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>FY2029</t>
+          <t>FY29</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -21475,12 +21475,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ORG_HILLSBOROUGH</t>
+          <t>ORG_HB</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -21528,7 +21528,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -21576,7 +21576,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>FY2026</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -21624,7 +21624,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -21672,7 +21672,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -21720,7 +21720,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -21768,7 +21768,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -21816,7 +21816,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">

--- a/data/exports/MFAS_Data_Warehouse.xlsx
+++ b/data/exports/MFAS_Data_Warehouse.xlsx
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6">
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20">
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -9458,7 +9458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9898,22 +9898,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Revenue by source</t>
+          <t>Wording — where figures come from</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Her words: "The broader view includes revenue from sources such as Grants, State, Other Funds, etc. So I want to make sure we have this broader view too."</t>
+          <t>The original sentence was not quite true and a sceptical reader could catch it: 40 of the 75 documents are the county's rather than the town's, and 14 of the 83 published figures come from the initiative's own request workbook — the administrative-spend series a commissioner supplied, and two capital-project cost changes. Each of those is already labelled where it appears, so the masthead was the only place that overclaimed. Changed rather than left, because the strongest sentence on the page is the worst one to have to walk back.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Work this project owes</t>
+          <t>Your decision</t>
         </is>
       </c>
     </row>
@@ -9930,22 +9930,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Stacked waterfall</t>
+          <t>Resident film</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Her stated preference for the visual, and her own Workbook B opens with a Budget Waterfall sheet.</t>
+          <t>It only appeared in the README before, where no resident will ever look. Placed as an offer on the judgement that a reader who arrives annoyed about a tax bill wants their own number first — but it is your film and the call is yours.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Work this project owes</t>
+          <t>Your decision</t>
         </is>
       </c>
     </row>
@@ -9962,7 +9962,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Total cost of ownership</t>
+          <t>Resident film</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -9970,10 +9970,14 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>The sentence was superseded because the site now publishes the audited record recovered from those scans. Nothing in the film's narration is wrong; it is one frame of a screenshot that no longer matches the page. Re-cutting means regenerating machine narration and music, so it is a cost and an ownership question rather than a fix this project should make unasked.</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Work this project owes</t>
+          <t>Your decision</t>
         </is>
       </c>
     </row>
@@ -9990,71 +9994,71 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>README film links if the repo moves</t>
+          <t>Revenue by source</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>They cannot be repo-relative: GitHub's blob viewer refuses the file outright ("we can't show files that are this big right now") and raw.githubusercontent serves it as application/octet-stream, which downloads instead of playing. Only Pages serves it as video/mp4 with Accept-Ranges. Measured, not assumed.</t>
+          <t>Her words: "The broader view includes revenue from sources such as Grants, State, Other Funds, etc. So I want to make sure we have this broader view too."</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Your decision</t>
+          <t>Work this project owes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Q024</t>
+          <t>Q020</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Driver: Salary and benefit increases</t>
+          <t>Stacked waterfall</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Her own follow-up against a $630,000 driver</t>
+          <t>Her stated preference for the visual, and her own Workbook B opens with a Budget Waterfall sheet.</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Records request to the Town</t>
+          <t>Work this project owes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Q025</t>
+          <t>Q021</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Driver: FY26 market pay adjustments</t>
+          <t>Total cost of ownership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -10062,31 +10066,27 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Her own follow-up against a $220,000 driver</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Records request to the Town</t>
+          <t>Work this project owes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Q026</t>
+          <t>Q022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Driver: Fire station reserve / future debt gap</t>
+          <t>README film links if the repo moves</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -10096,12 +10096,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Her own follow-up against a $370,000 driver</t>
+          <t>They cannot be repo-relative: GitHub's blob viewer refuses the file outright ("we can't show files that are this big right now") and raw.githubusercontent serves it as application/octet-stream, which downloads instead of playing. Only Pages serves it as video/mp4 with Accept-Ranges. Measured, not assumed.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Records request to the Town</t>
+          <t>Your decision</t>
         </is>
       </c>
     </row>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Driver: Ridgewalk Greenway reserve / future debt gap</t>
+          <t>Driver: Salary and benefit increases</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -10128,7 +10128,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Her own follow-up against a $337,000 driver</t>
+          <t>Her own follow-up against a $630,000 driver</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -10150,7 +10150,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Driver: Passenger rail / multi-modal station town share</t>
+          <t>Driver: FY26 market pay adjustments</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -10160,7 +10160,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Her own follow-up against a $3,500,000 driver</t>
+          <t>Her own follow-up against a $220,000 driver</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -10182,7 +10182,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Driver: Affordable housing annual contribution target</t>
+          <t>Driver: Fire station reserve / future debt gap</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -10192,7 +10192,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Her own follow-up against a $320,000 driver</t>
+          <t>Her own follow-up against a $370,000 driver</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -10214,7 +10214,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Driver: FY26 affordable housing major expense</t>
+          <t>Driver: Ridgewalk Greenway reserve / future debt gap</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -10224,7 +10224,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Her own follow-up against a $376,000 driver</t>
+          <t>Her own follow-up against a $337,000 driver</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Driver: Nonprofit partnership funding growth</t>
+          <t>Driver: Passenger rail / multi-modal station town share</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Her own follow-up against a $110,000 driver</t>
+          <t>Her own follow-up against a $3,500,000 driver</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -10278,7 +10278,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Driver: Public Space and Sustainability annual commitment</t>
+          <t>Driver: Affordable housing annual contribution target</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -10310,7 +10310,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Driver: Community Services reorganization</t>
+          <t>Driver: FY26 affordable housing major expense</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Her own follow-up against a $60,423 driver</t>
+          <t>Her own follow-up against a $376,000 driver</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -10342,7 +10342,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Driver: Police cameras and equipment</t>
+          <t>Driver: Nonprofit partnership funding growth</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -10352,7 +10352,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Her own follow-up against a $75,000 driver</t>
+          <t>Her own follow-up against a $110,000 driver</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Driver: Vehicle replacement funds</t>
+          <t>Driver: Public Space and Sustainability annual commitment</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -10384,7 +10384,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Her own follow-up against a $300,000 driver</t>
+          <t>Her own follow-up against a $320,000 driver</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Driver: Sales tax flatline</t>
+          <t>Driver: Community Services reorganization</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -10414,7 +10414,11 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Her own follow-up against a $60,423 driver</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>Records request to the Town</t>
@@ -10434,20 +10438,112 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
+          <t>Driver: Police cameras and equipment</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Her own follow-up against a $75,000 driver</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Records request to the Town</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Q038</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Driver: Vehicle replacement funds</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Her own follow-up against a $300,000 driver</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Records request to the Town</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Q039</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Driver: Sales tax flatline</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Records request to the Town</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Q040</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
           <t>Driver: Projected FY29 deficit</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Her own follow-up against a $-2,534,674 driver</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>Records request to the Town</t>
         </is>
@@ -10464,7 +10560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11114,32 +11210,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>pipeline</t>
+          <t>amy</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Revenue by source</t>
+          <t>Wording — where figures come from</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Build the broader revenue view she asked for — grants, state-shared revenue, other funds — not just property tax and sales tax.</t>
+          <t>The masthead used to read "Every figure comes from the town's own published documents". It now reads that every figure is shown with its document and page, and that the page says so on the spot wherever a figure comes from something other than a government's own publication. Is that the wording you want?</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>in progress</t>
+          <t>open</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Her words: "The broader view includes revenue from sources such as Grants, State, Other Funds, etc. So I want to make sure we have this broader view too."</t>
+          <t>The original sentence was not quite true and a sceptical reader could catch it: 40 of the 75 documents are the county's rather than the town's, and 14 of the 83 published figures come from the initiative's own request workbook — the administrative-spend series a commissioner supplied, and two capital-project cost changes. Each of those is already labelled where it appears, so the masthead was the only place that overclaimed. Changed rather than left, because the strongest sentence on the page is the worst one to have to walk back.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>her reply 2026-07-27</t>
+          <t>site audit 2026-07-28; enforced by tests/test_data_integrity.py::test_the_masthead_does_not_overclaim_where_figures_come_from</t>
         </is>
       </c>
     </row>
@@ -11151,32 +11247,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>pipeline</t>
+          <t>amy</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Stacked waterfall</t>
+          <t>Resident film</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Show the key drivers as a stacked waterfall of increases and decreases.</t>
+          <t>The 62-second film is now on the site itself, as a still image in the masthead that loads nothing until it is pressed. Should it stay an offer a reader can ignore, or lead the page?</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>in progress</t>
+          <t>open</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Her stated preference for the visual, and her own Workbook B opens with a Budget Waterfall sheet.</t>
+          <t>It only appeared in the README before, where no resident will ever look. Placed as an offer on the judgement that a reader who arrives annoyed about a tax bill wants their own number first — but it is your film and the call is yours.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>her reply 2026-07-27</t>
+          <t>site audit 2026-07-28</t>
         </is>
       </c>
     </row>
@@ -11188,17 +11284,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>pipeline</t>
+          <t>amy</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Total cost of ownership</t>
+          <t>Resident film</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>FY2028 and FY2029 do not exist as adopted rates. The town's capital plan states the tax rate its projects would require, which is a plan rather than a rate, and is reported separately as such.</t>
+          <t>At about 50 seconds the film shows a screenshot of the site carrying a sentence that has since been corrected — the old "nothing on this page is taken from those" line about scanned documents. Is that worth a re-cut?</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -11206,9 +11302,14 @@
           <t>open</t>
         </is>
       </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>The sentence was superseded because the site now publishes the audited record recovered from those scans. Nothing in the film's narration is wrong; it is one frame of a screenshot that no longer matches the page. Re-cutting means regenerating machine narration and music, so it is a cost and an ownership question rather than a fix this project should make unasked.</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>etl/s92_total_cost.py</t>
+          <t>site audit 2026-07-28</t>
         </is>
       </c>
     </row>
@@ -11220,32 +11321,32 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>amy</t>
+          <t>pipeline</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>README film links if the repo moves</t>
+          <t>Revenue by source</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>If this repository is transferred to another GitHub account, the two film links at the top of the README have to be updated — they are absolute Pages URLs.</t>
+          <t>Build the broader revenue view she asked for — grants, state-shared revenue, other funds — not just property tax and sales tax.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>in progress</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>They cannot be repo-relative: GitHub's blob viewer refuses the file outright ("we can't show files that are this big right now") and raw.githubusercontent serves it as application/octet-stream, which downloads instead of playing. Only Pages serves it as video/mp4 with Accept-Ranges. Measured, not assumed.</t>
+          <t>Her words: "The broader view includes revenue from sources such as Grants, State, Other Funds, etc. So I want to make sure we have this broader view too."</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>found 2026-07-28 when the blob link failed</t>
+          <t>her reply 2026-07-27</t>
         </is>
       </c>
     </row>
@@ -11257,37 +11358,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>david</t>
+          <t>pipeline</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Repository name</t>
+          <t>Stacked waterfall</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Rename the GitHub repository from `hoa-funds` to something that matches the project.</t>
+          <t>Show the key drivers as a stacked waterfall of increases and decreases.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>answered</t>
+          <t>in progress</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>The project is MFAS; "hoa" reads like a homeowners association and was the name of the empty repository this was first pushed into.</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Done 2026-07-28 — renamed to `MFAS`. git URLs redirect permanently; GitHub Pages does NOT, and Pages paths are case-sensitive, so the live address is https://oc-accountability.github.io/MFAS/ while both /hoa-funds/ and /mfas/ 404. Every link sent before the rename is dead and needs re-sending.</t>
+          <t>Her stated preference for the visual, and her own Workbook B opens with a Budget Waterfall sheet.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Amy 2026-07-27; renamed by David 2026-07-28</t>
+          <t>her reply 2026-07-27</t>
         </is>
       </c>
     </row>
@@ -11299,32 +11395,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>amy</t>
+          <t>pipeline</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Project dimension</t>
+          <t>Total cost of ownership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Should Project be a real dimension?</t>
+          <t>FY2028 and FY2029 do not exist as adopted rates. The town's capital plan states the tax rate its projects would require, which is a plan rather than a rate, and is reported separately as such.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>answered</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Yes — built in etl/s94_projects.py: 27 projects, $72.6M, each reconciled to its own printed totals.</t>
+          <t>open</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>asked 2026-07-26</t>
+          <t>etl/s92_total_cost.py</t>
         </is>
       </c>
     </row>
@@ -11341,27 +11432,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Recurring vs one-time</t>
+          <t>README film links if the repo moves</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Add a dimension separating ongoing operations from one-time items.</t>
+          <t>If this repository is transferred to another GitHub account, the two film links at the top of the README have to be updated — they are absolute Pages URLs.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>answered</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Built in etl/s88_mfas_dimensions.py. General Fund FY2027 is 86.6% recurring.</t>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>They cannot be repo-relative: GitHub's blob viewer refuses the file outright ("we can't show files that are this big right now") and raw.githubusercontent serves it as application/octet-stream, which downloads instead of playing. Only Pages serves it as video/mp4 with Accept-Ranges. Measured, not assumed.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>her instruction 2026-07-26</t>
+          <t>found 2026-07-28 when the blob link failed</t>
         </is>
       </c>
     </row>
@@ -11373,17 +11464,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>amy</t>
+          <t>david</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cross-fund transfers</t>
+          <t>Repository name</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>A schedule with the transfer columns going across.</t>
+          <t>Rename the GitHub repository from `hoa-funds` to something that matches the project.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -11391,14 +11482,19 @@
           <t>answered</t>
         </is>
       </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>The project is MFAS; "hoa" reads like a homeowners association and was the name of the empty repository this was first pushed into.</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Built in etl/s89_transfers.py, outgoing side only — the limitation is stated in the dataset.</t>
+          <t>Done 2026-07-28 — renamed to `MFAS`. git URLs redirect permanently; GitHub Pages does NOT, and Pages paths are case-sensitive, so the live address is https://oc-accountability.github.io/MFAS/ while both /hoa-funds/ and /mfas/ 404. Every link sent before the rename is dead and needs re-sending.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>her instruction 2026-07-26</t>
+          <t>Amy 2026-07-27; renamed by David 2026-07-28</t>
         </is>
       </c>
     </row>
@@ -11410,32 +11506,32 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>town</t>
+          <t>amy</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Driver: Salary and benefit increases</t>
+          <t>Project dimension</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Request department-by-department compensation growth and headcount/FTE history.</t>
+          <t>Should Project be a real dimension?</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Her own follow-up against a $630,000 driver</t>
+          <t>answered</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Yes — built in etl/s94_projects.py: 27 projects, $72.6M, each reconciled to its own printed totals.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Amy's v5 Audit Edition, Material_Change_Drivers</t>
+          <t>asked 2026-07-26</t>
         </is>
       </c>
     </row>
@@ -11447,32 +11543,32 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>town</t>
+          <t>amy</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Driver: FY26 market pay adjustments</t>
+          <t>Recurring vs one-time</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Clarify which departments received the largest pay adjustments.</t>
+          <t>Add a dimension separating ongoing operations from one-time items.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Her own follow-up against a $220,000 driver</t>
+          <t>answered</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Built in etl/s88_mfas_dimensions.py. General Fund FY2027 is 86.6% recurring.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Amy's v5 Audit Edition, Material_Change_Drivers</t>
+          <t>her instruction 2026-07-26</t>
         </is>
       </c>
     </row>
@@ -11484,32 +11580,32 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>town</t>
+          <t>amy</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Driver: Fire station reserve / future debt gap</t>
+          <t>Cross-fund transfers</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Ask for full station funding model and alternatives such as renovation.</t>
+          <t>A schedule with the transfer columns going across.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Her own follow-up against a $370,000 driver</t>
+          <t>answered</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Built in etl/s89_transfers.py, outgoing side only — the limitation is stated in the dataset.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Amy's v5 Audit Edition, Material_Change_Drivers</t>
+          <t>her instruction 2026-07-26</t>
         </is>
       </c>
     </row>
@@ -11526,12 +11622,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Driver: Ridgewalk Greenway reserve / future debt gap</t>
+          <t>Driver: Salary and benefit increases</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Ask if scope can be phased or outside funding increased.</t>
+          <t>Request department-by-department compensation growth and headcount/FTE history.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -11541,7 +11637,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Her own follow-up against a $337,000 driver</t>
+          <t>Her own follow-up against a $630,000 driver</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -11563,12 +11659,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Driver: Passenger rail / multi-modal station town share</t>
+          <t>Driver: FY26 market pay adjustments</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Ask for current project budget, funding agreements, and local match cap.</t>
+          <t>Clarify which departments received the largest pay adjustments.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -11578,7 +11674,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Her own follow-up against a $3,500,000 driver</t>
+          <t>Her own follow-up against a $220,000 driver</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -11600,12 +11696,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Driver: Affordable housing annual contribution target</t>
+          <t>Driver: Fire station reserve / future debt gap</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Track commitments by project, partner, year, and restricted vs unrestricted funds.</t>
+          <t>Ask for full station funding model and alternatives such as renovation.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -11615,7 +11711,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Her own follow-up against a $320,000 driver</t>
+          <t>Her own follow-up against a $370,000 driver</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -11637,12 +11733,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Driver: FY26 affordable housing major expense</t>
+          <t>Driver: Ridgewalk Greenway reserve / future debt gap</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Reconcile to affordable housing reserve and project-level commitments.</t>
+          <t>Ask if scope can be phased or outside funding increased.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -11652,7 +11748,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Her own follow-up against a $376,000 driver</t>
+          <t>Her own follow-up against a $337,000 driver</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -11674,12 +11770,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Driver: Nonprofit partnership funding growth</t>
+          <t>Driver: Passenger rail / multi-modal station town share</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Review whether increases should be frozen during projected deficits.</t>
+          <t>Ask for current project budget, funding agreements, and local match cap.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -11689,7 +11785,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Her own follow-up against a $110,000 driver</t>
+          <t>Her own follow-up against a $3,500,000 driver</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -11711,12 +11807,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Driver: Public Space and Sustainability annual commitment</t>
+          <t>Driver: Affordable housing annual contribution target</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Ask for a project list and measurable ROI/savings for sustainability funds.</t>
+          <t>Track commitments by project, partner, year, and restricted vs unrestricted funds.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -11748,12 +11844,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Driver: Community Services reorganization</t>
+          <t>Driver: FY26 affordable housing major expense</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ask for before/after org chart, net FTE change, and total savings.</t>
+          <t>Reconcile to affordable housing reserve and project-level commitments.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -11763,7 +11859,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Her own follow-up against a $60,423 driver</t>
+          <t>Her own follow-up against a $376,000 driver</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -11785,12 +11881,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Driver: Police cameras and equipment</t>
+          <t>Driver: Nonprofit partnership funding growth</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ask for Axon/Flock contract terms and renewal schedule.</t>
+          <t>Review whether increases should be frozen during projected deficits.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -11800,7 +11896,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Her own follow-up against a $75,000 driver</t>
+          <t>Her own follow-up against a $110,000 driver</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -11822,12 +11918,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Driver: Vehicle replacement funds</t>
+          <t>Driver: Public Space and Sustainability annual commitment</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Build a rolling vehicle replacement schedule by department.</t>
+          <t>Ask for a project list and measurable ROI/savings for sustainability funds.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -11837,7 +11933,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Her own follow-up against a $300,000 driver</t>
+          <t>Her own follow-up against a $320,000 driver</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -11859,17 +11955,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Driver: Sales tax flatline</t>
+          <t>Driver: Community Services reorganization</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Separate normal sales tax growth from COVID-era one-time growth and refunds.</t>
+          <t>Ask for before/after org chart, net FTE change, and total savings.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>open</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Her own follow-up against a $60,423 driver</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -11891,25 +11992,131 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
+          <t>Driver: Police cameras and equipment</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Ask for Axon/Flock contract terms and renewal schedule.</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Her own follow-up against a $75,000 driver</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Amy's v5 Audit Edition, Material_Change_Drivers</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Q038</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>town</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Driver: Vehicle replacement funds</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Build a rolling vehicle replacement schedule by department.</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Her own follow-up against a $300,000 driver</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Amy's v5 Audit Edition, Material_Change_Drivers</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Q039</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>town</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Driver: Sales tax flatline</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Separate normal sales tax growth from COVID-era one-time growth and refunds.</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Amy's v5 Audit Edition, Material_Change_Drivers</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Q040</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>town</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
           <t>Driver: Projected FY29 deficit</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>Build deficit bridge: personnel, debt, capital, revenue, policy choices.</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>Her own follow-up against a $-2,534,674 driver</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>Amy's v5 Audit Edition, Material_Change_Drivers</t>
         </is>
@@ -12131,7 +12338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I77"/>
+  <dimension ref="A1:I86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -13262,7 +13469,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>oc-design</t>
+          <t>municipal-finance-project-design-manual-v1-0</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -13272,7 +13479,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>OC Design.xlsx</t>
+          <t>Municipal Finance Project Design Manual v1.0.xlsx</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -13294,14 +13501,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>f66c9479c9ee9504…</t>
+          <t>1a917f31b130a274…</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>oc-pafr-2020</t>
+          <t>oc-design</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -13311,7 +13518,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>OC_PAFR_2020.pdf</t>
+          <t>OC Design.xlsx</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -13320,11 +13527,7 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>20 pages</t>
-        </is>
-      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>Machine-readable source</t>
@@ -13337,14 +13540,14 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>7f2bd6697b7d8550…</t>
+          <t>f66c9479c9ee9504…</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>orange-co-acfr-6-30-25final</t>
+          <t>oc-pafr-2020</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -13354,7 +13557,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Orange Co ACFR 6.30.25Final.pdf</t>
+          <t>OC_PAFR_2020.pdf</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -13365,7 +13568,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>231 pages</t>
+          <t>20 pages</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -13380,14 +13583,14 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>e962e7674ecad847…</t>
+          <t>7f2bd6697b7d8550…</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>orange-co-acfr-6-30-24-final</t>
+          <t>orange-co-acfr-6-30-25final</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13397,7 +13600,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Orange Co ACFR 6_30_24 Final_.pdf</t>
+          <t>Orange Co ACFR 6.30.25Final.pdf</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -13408,7 +13611,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>227 pages</t>
+          <t>231 pages</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -13423,14 +13626,14 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>cfb25d100dfe45b4…</t>
+          <t>e962e7674ecad847…</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>orange-county-2018-cafr</t>
+          <t>orange-co-acfr-6-30-24-final</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13440,7 +13643,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Orange County 2018 CAFR.pdf</t>
+          <t>Orange Co ACFR 6_30_24 Final_.pdf</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -13451,7 +13654,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>173 pages</t>
+          <t>227 pages</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -13466,14 +13669,14 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1146f1d25c6ea129…</t>
+          <t>cfb25d100dfe45b4…</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>orange-county-6-30-21-acfr-client-1</t>
+          <t>orange-county-2018-cafr</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -13483,7 +13686,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Orange County 6-30-21 ACFR - client_1.pdf</t>
+          <t>Orange County 2018 CAFR.pdf</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -13494,7 +13697,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>189 pages</t>
+          <t>173 pages</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -13509,14 +13712,14 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0793cd4978c0dab7…</t>
+          <t>1146f1d25c6ea129…</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>orange-county-6-30-21-compliance-report-client</t>
+          <t>orange-county-6-30-21-acfr-client-1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -13526,7 +13729,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Orange County 6-30-21 Compliance Report - client.pdf</t>
+          <t>Orange County 6-30-21 ACFR - client_1.pdf</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -13537,7 +13740,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>30 pages</t>
+          <t>189 pages</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -13552,14 +13755,14 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>6b4b31542848aa8d…</t>
+          <t>0793cd4978c0dab7…</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>orange-county-acfr-6-30-22-final-2</t>
+          <t>orange-county-6-30-21-compliance-report-client</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -13569,7 +13772,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Orange County ACFR 6.30.22 Final_2.pdf</t>
+          <t>Orange County 6-30-21 Compliance Report - client.pdf</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -13580,7 +13783,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>226 pages</t>
+          <t>30 pages</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -13595,14 +13798,14 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>f2bafc61c0929216…</t>
+          <t>6b4b31542848aa8d…</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>orange-county-cafr-6-30-20</t>
+          <t>orange-county-acfr-6-30-22-final-2</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -13612,7 +13815,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Orange County CAFR 6.30.20.pdf</t>
+          <t>Orange County ACFR 6.30.22 Final_2.pdf</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -13623,7 +13826,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>181 pages</t>
+          <t>226 pages</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -13638,14 +13841,14 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>e41a2c234f9d9a19…</t>
+          <t>f2bafc61c0929216…</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>orange-county-nc-acfr-6-30-23</t>
+          <t>orange-county-cafr-6-30-20</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -13655,7 +13858,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Orange County NC ACFR 6.30.23.pdf</t>
+          <t>Orange County CAFR 6.30.20.pdf</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -13666,7 +13869,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>227 pages</t>
+          <t>181 pages</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -13681,14 +13884,14 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>de96f5845a9ddc7a…</t>
+          <t>e41a2c234f9d9a19…</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>orange-county-municipal-finance-database-v1-0</t>
+          <t>orange-county-nc-acfr-6-30-23</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -13698,7 +13901,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Orange_County_Municipal_Finance_Database_v1.0.xlsx</t>
+          <t>Orange County NC ACFR 6.30.23.pdf</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -13707,7 +13910,11 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>227 pages</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>Machine-readable source</t>
@@ -13720,14 +13927,14 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>d819f7eab876f57d…</t>
+          <t>de96f5845a9ddc7a…</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>orange-county-municipal-finance-database-v1-1</t>
+          <t>orange-county-municipal-finance-database-v1-0</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -13737,7 +13944,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Orange_County_Municipal_Finance_Database_v1.1.xlsx</t>
+          <t>Orange_County_Municipal_Finance_Database_v1.0.xlsx</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -13759,14 +13966,14 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>359a2e63e4d0faea…</t>
+          <t>d819f7eab876f57d…</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>orange-county-municipal-financial-data-warehouse-v1-2</t>
+          <t>orange-county-municipal-finance-database-v1-1</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -13776,7 +13983,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Orange_County_Municipal_Financial_Data_Warehouse_v1.2.xlsx</t>
+          <t>Orange_County_Municipal_Finance_Database_v1.1.xlsx</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -13798,14 +14005,14 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>8ca50c7d1d9b59ae…</t>
+          <t>359a2e63e4d0faea…</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>orange-county-municipal-financial-data-warehouse-v2-0</t>
+          <t>orange-county-municipal-financial-data-warehouse-v1-2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -13815,7 +14022,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Orange_County_Municipal_Financial_Data_Warehouse_v2.0.xlsx</t>
+          <t>Orange_County_Municipal_Financial_Data_Warehouse_v1.2.xlsx</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -13837,14 +14044,14 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>d1c0019c2745468a…</t>
+          <t>8ca50c7d1d9b59ae…</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>orange-county-municipal-financial-information-system-v2-2-foundation</t>
+          <t>orange-county-municipal-financial-data-warehouse-v2-0</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -13854,7 +14061,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Orange_County_Municipal_Financial_Information_System_v2.2_Foundation.xlsx</t>
+          <t>Orange_County_Municipal_Financial_Data_Warehouse_v2.0.xlsx</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -13876,14 +14083,14 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>600ff180a3e058b3…</t>
+          <t>d1c0019c2745468a…</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>redatarequestlongtermfiscaltrendandsustainability</t>
+          <t>orange-county-municipal-financial-information-system-v2-2-foundation</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -13893,13 +14100,13 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>redatarequestlongtermfiscaltrendandsustainability.zip</t>
+          <t>Orange_County_Municipal_Financial_Information_System_v2.2_Foundation.xlsx</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Financial-Report</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -13915,41 +14122,33 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>c7b6ae4934174283…</t>
+          <t>600ff180a3e058b3…</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>affordable-housing-fy18-fy29-in-pdf</t>
+          <t>redatarequestlongtermfiscaltrendandsustainability</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ORG_HB</t>
+          <t>ORG_OC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Affordable Housing (FY18-FY29) in pdf.pdf</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>FY18</t>
-        </is>
-      </c>
+          <t>redatarequestlongtermfiscaltrendandsustainability.zip</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>Financial-Report</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>1 pages</t>
-        </is>
-      </c>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
           <t>Machine-readable source</t>
@@ -13962,14 +14161,14 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>7846cdb939c763c1…</t>
+          <t>c7b6ae4934174283…</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>annual-comprehensive-financial-report-year-ended-june-30-2018</t>
+          <t>affordable-housing-fy18-fy29-in-pdf</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -13979,7 +14178,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Annual Comprehensive Financial Report Year Ended June 30, 2018.pdf</t>
+          <t>Affordable Housing (FY18-FY29) in pdf.pdf</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -13994,29 +14193,29 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>175 pages</t>
+          <t>1 pages</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Excluded from extraction — scanned</t>
+          <t>Machine-readable source</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>578ef6226a5a9065…</t>
+          <t>7846cdb939c763c1…</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>annual-comprehensive-financial-report-year-ended-june-30-2019</t>
+          <t>annual-comprehensive-financial-report-year-ended-june-30-2018</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -14026,12 +14225,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Annual Comprehensive Financial Report Year Ended June 30, 2019.pdf</t>
+          <t>Annual Comprehensive Financial Report Year Ended June 30, 2018.pdf</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>FY19</t>
+          <t>FY18</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -14041,7 +14240,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>181 pages</t>
+          <t>175 pages</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -14056,14 +14255,14 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>846b43a917b02dd1…</t>
+          <t>578ef6226a5a9065…</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>annual-comprehensive-financial-report-year-ended-june-30-2020</t>
+          <t>annual-comprehensive-financial-report-year-ended-june-30-2019</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -14073,12 +14272,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Annual Comprehensive Financial Report Year Ended June 30, 2020.pdf</t>
+          <t>Annual Comprehensive Financial Report Year Ended June 30, 2019.pdf</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>FY20</t>
+          <t>FY19</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -14088,7 +14287,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>163 pages</t>
+          <t>181 pages</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -14103,14 +14302,14 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>b9a958bcede6b1aa…</t>
+          <t>846b43a917b02dd1…</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>annual-comprehensive-financial-report-year-ended-june-30-2021</t>
+          <t>annual-comprehensive-financial-report-year-ended-june-30-2020</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -14120,12 +14319,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Annual Comprehensive Financial Report Year Ended June 30, 2021.pdf</t>
+          <t>Annual Comprehensive Financial Report Year Ended June 30, 2020.pdf</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>FY21</t>
+          <t>FY20</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -14135,7 +14334,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>127 pages</t>
+          <t>163 pages</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -14150,14 +14349,14 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>974877e4eaf280e8…</t>
+          <t>b9a958bcede6b1aa…</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>annual-financial-report-year-ended-june-30-2022</t>
+          <t>annual-comprehensive-financial-report-year-ended-june-30-2021</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -14167,12 +14366,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Annual Financial Report_ Year Ended June 30, 2022.pdf</t>
+          <t>Annual Comprehensive Financial Report Year Ended June 30, 2021.pdf</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>FY22</t>
+          <t>FY21</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -14182,7 +14381,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>130 pages</t>
+          <t>127 pages</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -14197,14 +14396,14 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>fa78d495e724b136…</t>
+          <t>974877e4eaf280e8…</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>annual-financial-report-year-ended-june-30-2023</t>
+          <t>annual-financial-report-year-ended-june-30-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -14214,12 +14413,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Annual Financial Report_ Year Ended June 30, 2023.pdf</t>
+          <t>Annual Financial Report_ Year Ended June 30, 2022.pdf</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>FY23</t>
+          <t>FY22</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -14229,7 +14428,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>141 pages</t>
+          <t>130 pages</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -14244,14 +14443,14 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>b3413df16b3a701b…</t>
+          <t>fa78d495e724b136…</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>annual-financial-report-year-ended-june-30-2024</t>
+          <t>annual-financial-report-year-ended-june-30-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -14261,12 +14460,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Annual Financial Report_ Year Ended June 30, 2024.pdf</t>
+          <t>Annual Financial Report_ Year Ended June 30, 2023.pdf</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>FY24</t>
+          <t>FY23</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -14276,7 +14475,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>139 pages</t>
+          <t>141 pages</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -14291,14 +14490,14 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>dd2892d97a2e9ab8…</t>
+          <t>b3413df16b3a701b…</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>annual-financial-report-year-ended-june-30-2025</t>
+          <t>annual-financial-report-year-ended-june-30-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -14308,12 +14507,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Annual Financial Report_ Year Ended June 30, 2025.pdf</t>
+          <t>Annual Financial Report_ Year Ended June 30, 2024.pdf</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>FY25</t>
+          <t>FY24</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -14323,7 +14522,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>131 pages</t>
+          <t>139 pages</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -14338,14 +14537,14 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>8a18342afb8bd4a4…</t>
+          <t>dd2892d97a2e9ab8…</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>comprehensive-annual-financial-report-fy18</t>
+          <t>annual-financial-report-year-ended-june-30-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -14355,12 +14554,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Comprehensive Annual Financial Report (FY18).pdf</t>
+          <t>Annual Financial Report_ Year Ended June 30, 2025.pdf</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>FY18</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -14370,7 +14569,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>175 pages</t>
+          <t>131 pages</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -14385,14 +14584,14 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>c05c734930d3101b…</t>
+          <t>8a18342afb8bd4a4…</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>comprehensive-sustainability-plan-community-visioning-survey-summary-20230530</t>
+          <t>comprehensive-annual-financial-report-fy18</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -14402,10 +14601,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Comprehensive Sustainability Plan Community Visioning Survey Summary 20230530.pdf</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>Comprehensive Annual Financial Report (FY18).pdf</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>FY18</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>Financial-Report</t>
@@ -14413,29 +14616,29 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>22 pages</t>
+          <t>175 pages</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Machine-readable source</t>
+          <t>Excluded from extraction — scanned</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>57fda6b9e4a80a36…</t>
+          <t>c05c734930d3101b…</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>debt-schedules-from-hillsborough-fd</t>
+          <t>comprehensive-sustainability-plan-community-visioning-survey-summary-20230530</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -14445,7 +14648,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Debt Schedules from Hillsborough FD.docx</t>
+          <t>Comprehensive Sustainability Plan Community Visioning Survey Summary 20230530.pdf</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -14454,7 +14657,11 @@
           <t>Financial-Report</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>22 pages</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr">
         <is>
           <t>Machine-readable source</t>
@@ -14467,14 +14674,14 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>4066745db57ba17d…</t>
+          <t>57fda6b9e4a80a36…</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>debt-service-projections</t>
+          <t>debt-schedules-from-hillsborough-fd</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -14484,7 +14691,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Debt Service Projections.xlsx</t>
+          <t>Debt Schedules from Hillsborough FD.docx</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -14506,14 +14713,14 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>efc644db8b5d2c52…</t>
+          <t>4066745db57ba17d…</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>effect-of-debt-management</t>
+          <t>debt-service-projections</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -14523,20 +14730,16 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Effect of Debt Management.pdf</t>
+          <t>Debt Service Projections.xlsx</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Budget</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2 pages</t>
-        </is>
-      </c>
+          <t>Financial-Report</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
           <t>Machine-readable source</t>
@@ -14549,14 +14752,14 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>229261477c537e38…</t>
+          <t>efc644db8b5d2c52…</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>fy26-budget-message</t>
+          <t>effect-of-debt-management</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -14566,14 +14769,10 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FY26 Budget Message.pdf</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>FY26</t>
-        </is>
-      </c>
+          <t>Effect of Debt Management.pdf</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t>Budget</t>
@@ -14581,7 +14780,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>14 pages</t>
+          <t>2 pages</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -14596,14 +14795,14 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>104b3ff80f163a6e…</t>
+          <t>229261477c537e38…</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>fy26-budget-ordinance</t>
+          <t>fy26-budget-message</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -14613,7 +14812,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>FY26 Budget Ordinance.pdf</t>
+          <t>FY26 Budget Message.pdf</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -14623,12 +14822,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Financial-Report</t>
+          <t>Budget</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>3 pages</t>
+          <t>14 pages</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -14643,14 +14842,14 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>fbfbdcff2347705b…</t>
+          <t>104b3ff80f163a6e…</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>fy26-budget-and-financial-plan-adopted</t>
+          <t>fy26-budget-ordinance</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -14660,7 +14859,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>FY26 Budget and Financial Plan Adopted.pdf</t>
+          <t>FY26 Budget Ordinance.pdf</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -14670,12 +14869,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Budget</t>
+          <t>Financial-Report</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>234 pages</t>
+          <t>3 pages</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -14690,14 +14889,14 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>24e90511ef2250da…</t>
+          <t>fbfbdcff2347705b…</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>fy26-recommended-budget-and-financial-plan</t>
+          <t>fy26-budget-and-financial-plan-adopted</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -14707,7 +14906,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FY26 Recommended Budget and Financial Plan.pdf</t>
+          <t>FY26 Budget and Financial Plan Adopted.pdf</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -14722,7 +14921,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>295 pages</t>
+          <t>234 pages</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -14737,14 +14936,14 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2efdb212759e171b…</t>
+          <t>24e90511ef2250da…</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>fy27-budget-message</t>
+          <t>fy26-recommended-budget-and-financial-plan</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -14754,12 +14953,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>FY27 Budget Message.pdf</t>
+          <t>FY26 Recommended Budget and Financial Plan.pdf</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>FY27</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -14769,7 +14968,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>7 pages</t>
+          <t>295 pages</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -14784,14 +14983,14 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>bea2836db7541b06…</t>
+          <t>2efdb212759e171b…</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>fy27-budget-and-financial-plan-recommended</t>
+          <t>fy27-budget-message</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -14801,7 +15000,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>FY27 Budget and Financial Plan Recommended.pdf</t>
+          <t>FY27 Budget Message.pdf</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -14816,7 +15015,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>280 pages</t>
+          <t>7 pages</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -14831,14 +15030,14 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>9e6747e1ce1448b8…</t>
+          <t>bea2836db7541b06…</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>fiscal-year-2024-2026-strategic-plan-20230626</t>
+          <t>fy27-budget-and-financial-plan-recommended</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -14848,12 +15047,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Fiscal Year 2024 2026 Strategic Plan 20230626.pdf</t>
+          <t>FY27 Budget and Financial Plan Recommended.pdf</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>FY24</t>
+          <t>FY27</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -14863,29 +15062,29 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>16 pages</t>
+          <t>280 pages</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Excluded from extraction — scanned</t>
+          <t>Machine-readable source</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>286a81033d750f8d…</t>
+          <t>9e6747e1ce1448b8…</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>fiscal-year-2025-budget-message</t>
+          <t>fiscal-year-2024-2026-strategic-plan-20230626</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -14895,12 +15094,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Fiscal Year 2025 Budget Message.pdf</t>
+          <t>Fiscal Year 2024 2026 Strategic Plan 20230626.pdf</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>FY25</t>
+          <t>FY24</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -14910,29 +15109,29 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>18 pages</t>
+          <t>16 pages</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Machine-readable source</t>
+          <t>Excluded from extraction — scanned</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>fdf8217b826b6e06…</t>
+          <t>286a81033d750f8d…</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>fiscal-year-2025-financial-report</t>
+          <t>fiscal-year-2025-budget-message</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -14942,7 +15141,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Fiscal Year 2025 Financial Report.pdf</t>
+          <t>Fiscal Year 2025 Budget Message.pdf</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -14957,7 +15156,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>131 pages</t>
+          <t>18 pages</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -14972,14 +15171,14 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>8b60dad6367d4d3b…</t>
+          <t>fdf8217b826b6e06…</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>fiscal-year-2025-managers-recommended-budget-and-financial-work-plan</t>
+          <t>fiscal-year-2025-financial-report</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -14989,7 +15188,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Fiscal Year 2025 Managers Recommended Budget and Financial Work Plan.pdf</t>
+          <t>Fiscal Year 2025 Financial Report.pdf</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -15004,7 +15203,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>274 pages</t>
+          <t>131 pages</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -15019,14 +15218,14 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>1e6ac56bed6a6119…</t>
+          <t>8b60dad6367d4d3b…</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>hillsborough-data-request-june-2027</t>
+          <t>fiscal-year-2025-managers-recommended-budget-and-financial-work-plan</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -15036,16 +15235,24 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Hillsborough Data Request June 2027.xlsx</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
+          <t>Fiscal Year 2025 Managers Recommended Budget and Financial Work Plan.pdf</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>FY25</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Records-Request</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr"/>
+          <t>Budget</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>274 pages</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr">
         <is>
           <t>Machine-readable source</t>
@@ -15058,14 +15265,14 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>290fca8aac4dd0f3…</t>
+          <t>1e6ac56bed6a6119…</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>hillsborough-gf-trend-schedules-fy18-fy27-v5-audit-edition</t>
+          <t>hillsborough-data-request-june-2027</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -15075,13 +15282,13 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Hillsborough_GF_Trend_Schedules_FY18_FY27_v5_Audit_Edition.xlsx</t>
+          <t>Hillsborough Data Request June 2027.xlsx</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Financial-Report</t>
+          <t>Records-Request</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
@@ -15097,14 +15304,14 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>f2b817694d6dbeab…</t>
+          <t>290fca8aac4dd0f3…</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>hillsborough-rateoptions-22326-1</t>
+          <t>hillsborough-gf-trend-schedules-fy18-fy27</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -15114,20 +15321,16 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Hillsborough_RateOptions_22326 1.pdf</t>
+          <t>Hillsborough_GF_Trend_Schedules_FY18_FY27.xlsx</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Budget</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>30 pages</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
           <t>Machine-readable source</t>
@@ -15140,14 +15343,14 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>f680cee67b886337…</t>
+          <t>a4cff7456c4ca7f8…</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>hillsborough-workbook-b-fiscal-sustainability-risk-model</t>
+          <t>hillsborough-gf-trend-schedules-fy18-fy27-v2</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -15157,13 +15360,13 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hillsborough_Workbook_B_Fiscal_Sustainability_Risk_Model.xlsx</t>
+          <t>Hillsborough_GF_Trend_Schedules_FY18_FY27_v2.xlsx</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Financial-Report</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
@@ -15179,14 +15382,14 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>f6fa0e0de53756ea…</t>
+          <t>b29c95ce9728c4c8…</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>item-attachment-003-f0fc06314ce6427399e71e8d4d799c09</t>
+          <t>hillsborough-gf-trend-schedules-fy18-fy27-v3</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -15196,20 +15399,16 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ITEM-Attachment-003-f0fc06314ce6427399e71e8d4d799c09.pdf</t>
+          <t>Hillsborough_GF_Trend_Schedules_FY18_FY27_v3.xlsx</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Budget</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>72 pages</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
           <t>Machine-readable source</t>
@@ -15222,14 +15421,14 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>6decc5fca848a1be…</t>
+          <t>b27792f954004d28…</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>oc-hillsborough-fiscal-analysis-project</t>
+          <t>hillsborough-gf-trend-schedules-fy18-fy27-v4</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -15239,7 +15438,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>OC &amp; Hillsborough Fiscal Analysis Project.docx</t>
+          <t>Hillsborough_GF_Trend_Schedules_FY18_FY27_v4.xlsx</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -15261,14 +15460,14 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>7ff6409f36a3503b…</t>
+          <t>fdf1cc1614ccf061…</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>organizational-chart-of-town-services-and-administration-20230106</t>
+          <t>hillsborough-gf-trend-schedules-fy18-fy27-v5-audit-edition</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -15278,20 +15477,16 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Organizational Chart of Town Services and Administration 20230106.pdf</t>
+          <t>Hillsborough_GF_Trend_Schedules_FY18_FY27_v5_Audit_Edition.xlsx</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Budget</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>1 pages</t>
-        </is>
-      </c>
+          <t>Financial-Report</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
           <t>Machine-readable source</t>
@@ -15304,14 +15499,14 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>0ea1fa2f88125d04…</t>
+          <t>f2b817694d6dbeab…</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>recommended-fy27budgetataglanceflyer</t>
+          <t>hillsborough-municipal-financial-database-v1</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -15321,20 +15516,16 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Recommended FY27BudgetAtAGlanceFlyer.pdf</t>
+          <t>Hillsborough_Municipal_Financial_Database_v1.xlsx</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Budget</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>1 pages</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
           <t>Machine-readable source</t>
@@ -15347,14 +15538,14 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>b1aef110d4229f1d…</t>
+          <t>e20884babf4cf058…</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>sales-tax-information</t>
+          <t>hillsborough-municipal-financial-database-v2-fy18-fy29</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -15364,7 +15555,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Sales Tax Information.docx</t>
+          <t>Hillsborough_Municipal_Financial_Database_v2_FY18_FY29.xlsx</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -15386,14 +15577,14 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>60ec376a43d36307…</t>
+          <t>9571b92d98c92778…</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>stormwater-presentation-202404</t>
+          <t>hillsborough-rateoptions-22326-1</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -15403,7 +15594,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Stormwater Presentation 202404.pdf</t>
+          <t>Hillsborough_RateOptions_22326 1.pdf</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -15414,7 +15605,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>14 pages</t>
+          <t>30 pages</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -15429,14 +15620,14 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>816c7eaa0623fddd…</t>
+          <t>f680cee67b886337…</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>water-and-sewer-utility-rate-study-20240531</t>
+          <t>hillsborough-workbook-b-fiscal-sustainability-risk-model</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -15446,31 +15637,398 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Water and Sewer Utility Rate Study 20240531.pdf</t>
+          <t>Hillsborough_Workbook_B_Fiscal_Sustainability_Risk_Model.xlsx</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
+          <t>Financial-Report</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Machine-readable source</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>f6fa0e0de53756ea…</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>item-attachment-003-f0fc06314ce6427399e71e8d4d799c09</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>ORG_HB</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ITEM-Attachment-003-f0fc06314ce6427399e71e8d4d799c09.pdf</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
           <t>Budget</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>72 pages</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Machine-readable source</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>6decc5fca848a1be…</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>municipal-finance-database-hillsborough-v1-0</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>ORG_HB</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Municipal Finance Database - Hillsborough - v1.0.xlsx</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Machine-readable source</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>f2dacd7ae4b1b77b…</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>municipal-financial-analysis-hillsborough-v1-0</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>ORG_HB</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Municipal Financial Analysis - Hillsborough - v1.0.xlsx</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Machine-readable source</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>ddcc9730385f52d7…</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>oc-hillsborough-fiscal-analysis-project</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>ORG_HB</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>OC &amp; Hillsborough Fiscal Analysis Project.docx</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Machine-readable source</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>7ff6409f36a3503b…</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>organizational-chart-of-town-services-and-administration-20230106</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>ORG_HB</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Organizational Chart of Town Services and Administration 20230106.pdf</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Budget</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>1 pages</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Machine-readable source</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>0ea1fa2f88125d04…</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>recommended-fy27budgetataglanceflyer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>ORG_HB</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Recommended FY27BudgetAtAGlanceFlyer.pdf</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Budget</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>1 pages</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Machine-readable source</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>b1aef110d4229f1d…</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>sales-tax-information</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>ORG_HB</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Sales Tax Information.docx</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Machine-readable source</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>60ec376a43d36307…</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>stormwater-presentation-202404</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>ORG_HB</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Stormwater Presentation 202404.pdf</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Budget</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>14 pages</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Machine-readable source</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>816c7eaa0623fddd…</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>water-and-sewer-utility-rate-study-20240531</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>ORG_HB</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Water and Sewer Utility Rate Study 20240531.pdf</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Budget</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
         <is>
           <t>27 pages</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>Machine-readable source</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
         <is>
           <t>d113a20dca03f82e…</t>
         </is>

--- a/data/exports/MFAS_Data_Warehouse.xlsx
+++ b/data/exports/MFAS_Data_Warehouse.xlsx
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -8631,7 +8631,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1031</v>
+        <v>679</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9908,7 +9908,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>The original sentence was not quite true and a sceptical reader could catch it: 40 of the 75 documents are the county's rather than the town's, and 14 of the 83 published figures come from the initiative's own request workbook — the administrative-spend series a commissioner supplied, and two capital-project cost changes. Each of those is already labelled where it appears, so the masthead was the only place that overclaimed. Changed rather than left, because the strongest sentence on the page is the worst one to have to walk back.</t>
+          <t>The original sentence was not quite true and a sceptical reader could catch it: 31 of the 84 documents concern Orange County rather than the town, and 14 of the 83 published figures come from the initiative's own request workbook — the administrative-spend series a commissioner supplied, and two capital-project cost changes. Each of those is already labelled where it appears. (The masthead was not the only place: the page's meta description carried the same claim and was corrected separately.) Changed rather than left, because the strongest sentence on the page is the worst one to have to walk back.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -9972,7 +9972,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>The sentence was superseded because the site now publishes the audited record recovered from those scans. Nothing in the film's narration is wrong; it is one frame of a screenshot that no longer matches the page. Re-cutting means regenerating machine narration and music, so it is a cost and an ownership question rather than a fix this project should make unasked.</t>
+          <t>The sentence was superseded because the site now publishes the audited record recovered from those scans. Since this was first raised, a second audit widened it: the narration itself says at ~49s that "Every figure names the document and the page it came from", which overpromises the same way the old masthead did (14 figures come from spreadsheet cells that have no page); and the film's "2 governments / 6 documents / 1,031 pages" hold shows counts that changed when the archive's duplicate county budget stopped being counted twice (now 5 documents, 679 pages — the masthead card was switched to the film's opening question so the stale figures no longer sit on the front page, but they remain inside the film). Re-cutting means regenerating machine narration and music, so it is a cost and an ownership question rather than a fix this project should make unasked.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -10546,6 +10546,166 @@
       <c r="F34" t="inlineStr">
         <is>
           <t>Records request to the Town</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>County workbook — Source_Register alignment</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>The county table's figures are yours and are published as yours, but only FY2018's row can currently be re-verified against a held report. Aligning the register makes every year checkable the way FY2018 already is.</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Your decision</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Dam Repairs — funding vs expenditure totals</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Both tables are printed in the same document and both add up internally, so this is a question about the document rather than an extraction error — exactly the kind of difference a resident checking the numbers would find.</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Records request to the Town</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Question-register id stability</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Amy asked for this register specifically to track her open questions; an id that silently changes meaning defeats that. Append-only is the interim rule as of this audit, but it relies on discipline rather than the generator.</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Repository owner action</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Q044</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Wording — who adopts the budget</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>A claim about who exercises a power is the kind a resident can check against the town charter, and the archive cannot settle it either way — so it is flagged rather than silently rewritten.</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Your decision</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Q045</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Stormwater Fund reconciliation checks</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>A fund with no checks is indistinguishable on screen from a fund that failed them. The explorer now says so explicitly, but the honest fix is to run the checks.</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Work this project owes</t>
         </is>
       </c>
     </row>
@@ -10560,7 +10720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11230,7 +11390,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>The original sentence was not quite true and a sceptical reader could catch it: 40 of the 75 documents are the county's rather than the town's, and 14 of the 83 published figures come from the initiative's own request workbook — the administrative-spend series a commissioner supplied, and two capital-project cost changes. Each of those is already labelled where it appears, so the masthead was the only place that overclaimed. Changed rather than left, because the strongest sentence on the page is the worst one to have to walk back.</t>
+          <t>The original sentence was not quite true and a sceptical reader could catch it: 31 of the 84 documents concern Orange County rather than the town, and 14 of the 83 published figures come from the initiative's own request workbook — the administrative-spend series a commissioner supplied, and two capital-project cost changes. Each of those is already labelled where it appears. (The masthead was not the only place: the page's meta description carried the same claim and was corrected separately.) Changed rather than left, because the strongest sentence on the page is the worst one to have to walk back.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -11304,12 +11464,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>The sentence was superseded because the site now publishes the audited record recovered from those scans. Nothing in the film's narration is wrong; it is one frame of a screenshot that no longer matches the page. Re-cutting means regenerating machine narration and music, so it is a cost and an ownership question rather than a fix this project should make unasked.</t>
+          <t>The sentence was superseded because the site now publishes the audited record recovered from those scans. Since this was first raised, a second audit widened it: the narration itself says at ~49s that "Every figure names the document and the page it came from", which overpromises the same way the old masthead did (14 figures come from spreadsheet cells that have no page); and the film's "2 governments / 6 documents / 1,031 pages" hold shows counts that changed when the archive's duplicate county budget stopped being counted twice (now 5 documents, 679 pages — the masthead card was switched to the film's opening question so the stale figures no longer sit on the front page, but they remain inside the film). Re-cutting means regenerating machine narration and music, so it is a cost and an ownership question rather than a fix this project should make unasked.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>site audit 2026-07-28</t>
+          <t>site audit 2026-07-28; widened by the second-pass audit 2026-07-28</t>
         </is>
       </c>
     </row>
@@ -12119,6 +12279,191 @@
       <c r="H42" t="inlineStr">
         <is>
           <t>Amy's v5 Audit Edition, Material_Change_Drivers</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>amy</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>County workbook — Source_Register alignment</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Six of the eight county summary rows the site shows (Source_IDs OC_ACFR_2021 through OC_ACFR_2025, and OC_CAFR_2019) cite reports that are not in your workbook's own Source_Register, so this build cannot resolve them to a held file and re-check the figures. The FY2019 CAFR itself is not in the archive at all. Could the Source_Register gain rows for those years — and do you have the FY2019 CAFR to add?</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>The county table's figures are yours and are published as yours, but only FY2018's row can currently be re-verified against a held report. Aligning the register makes every year checkable the way FY2018 already is.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>second-pass audit 2026-07-28; measured by etl/s85_warehouse.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>town</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Dam Repairs — funding vs expenditure totals</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>In the FY27 capital plan, the Dam Repairs project's funding sources total $2,915,840 while its expenditures total $2,861,320 — funding exceeds spending by $54,520, and each table reconciles to its own printed total. Which figure is authoritative, and what does the $54,520 difference represent?</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Both tables are printed in the same document and both add up internally, so this is a question about the document rather than an extraction error — exactly the kind of difference a resident checking the numbers would find.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>second-pass audit 2026-07-28; measured from data/datasets/projects.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>david</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Question-register id stability</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Register ids are sequence positions, so inserting an item renumbers every later one — the 2026-07-28 insertions moved Q019 to Q022, and any Q-number cited in an earlier email now points at a different question. Should ids become stable slugs (breaking all existing references once), or stay positional with a rule that new items only ever append?</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Amy asked for this register specifically to track her open questions; an id that silently changes meaning defeats that. Append-only is the interim rule as of this audit, but it relies on discipline rather than the generator.</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>second-pass audit 2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Q044</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>amy</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Wording — who adopts the budget</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>The speak-up section used to say the budget is adopted by "the mayor and Board of Commissioners". No document in the archive states the adoption mechanics, and in NC towns the board ordinarily adopts with the mayor voting only to break ties — so the sentence now says "the town's governing board", which is true on any reading. Should it name the Board of Commissioners alone, or is the mayor part of adoption here?</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>A claim about who exercises a power is the kind a resident can check against the town charter, and the archive cannot settle it either way — so it is flagged rather than silently rewritten.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>second-pass audit 2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Q045</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>pipeline</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Stormwater Fund reconciliation checks</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>The spending explorer's reconciliation gate covers the General Fund and Water &amp; Sewer (30 checks each) but emits no checks at all for the Stormwater Fund, so its slices render with no verification statement either way. Emit Stormwater checks in stage 50 from the appendix's own category totals.</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>A fund with no checks is indistinguishable on screen from a fund that failed them. The explorer now says so explicitly, but the honest fix is to run the checks.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>second-pass audit 2026-07-28; measured from data/datasets/lineitem_validation.json</t>
         </is>
       </c>
     </row>
@@ -12235,7 +12580,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -12313,7 +12658,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -12409,7 +12754,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4-b-cip-presentation</t>
+          <t>architecture-design-specification</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -12419,7 +12764,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4-b - CIP Presentation.pdf</t>
+          <t>Architecture &amp; Design Specification.docx</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -12428,11 +12773,7 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>22 pages</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Machine-readable source</t>
@@ -12445,14 +12786,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3dc0fef3cdf0c2a8…</t>
+          <t>cffc8ba7be2578fa…</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4-b-1-county-managers-cip-transmittal-letter-final</t>
+          <t>architecture-design-specification-2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -12462,7 +12803,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4-b 1 - County Managers CIP Transmittal Letter - FINAL.pdf</t>
+          <t>Architecture &amp; Design Specification.pdf</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -12473,7 +12814,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>16 pages</t>
+          <t>13 pages</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -12488,14 +12829,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5f2158d47bc5d5a0…</t>
+          <t>adc8c4ccfb6ac00b…</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>appendix-a-county-profile-data-element-pdf</t>
+          <t>decision-context-model-pptx</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -12505,7 +12846,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Appendix A_ County Profile (Data) Element (PDF).pdf</t>
+          <t>Decision Context Model.pptx</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -12514,11 +12855,7 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>100 pages</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Machine-readable source</t>
@@ -12531,14 +12868,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1de901e83a325591…</t>
+          <t>42c67c7ff8bd7ed2…</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>architecture-design-specification</t>
+          <t>issues-log</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -12548,13 +12885,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Architecture &amp; Design Specification.docx</t>
+          <t>Issues Log.xlsx</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Issues</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -12570,14 +12907,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>cffc8ba7be2578fa…</t>
+          <t>e43269868eb341b3…</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>architecture-design-specification-2</t>
+          <t>mfas-architecture-notebook</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -12587,7 +12924,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Architecture &amp; Design Specification.pdf</t>
+          <t>MFAS Architecture Notebook.docx</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -12596,11 +12933,7 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>13 pages</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Machine-readable source</t>
@@ -12613,14 +12946,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>adc8c4ccfb6ac00b…</t>
+          <t>545f29f4d95ffec5…</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>budget-ordinance-fy2025-26</t>
+          <t>mfas-architecture-notebook-2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -12630,14 +12963,10 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Budget Ordinance FY2025-26.pdf</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>FY25</t>
-        </is>
-      </c>
+          <t>MFAS Architecture Notebook.pdf</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Other</t>
@@ -12645,7 +12974,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>14 pages</t>
+          <t>18 pages</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -12660,14 +12989,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5048fa9fae4e6313…</t>
+          <t>c2ad4c28ca659cc1…</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>decision-context-model-pptx</t>
+          <t>mfas-conceptual-architecture</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -12677,7 +13006,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Decision Context Model.pptx</t>
+          <t>MFAS Conceptual Architecture.docx</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -12699,14 +13028,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>42c67c7ff8bd7ed2…</t>
+          <t>7fc6ceb2b9492b20…</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>fy-2018-19-annual-financial-report</t>
+          <t>mfas-conceptual-architecture-2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -12716,14 +13045,10 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FY 2018-19 Annual Financial Report.pdf</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>FY18</t>
-        </is>
-      </c>
+          <t>MFAS Conceptual Architecture.pdf</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>Other</t>
@@ -12731,7 +13056,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>182 pages</t>
+          <t>19 pages</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -12746,14 +13071,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>606601997980895e…</t>
+          <t>6071c5d487b22b70…</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>fy-2018-19-popular-annual-financial-report</t>
+          <t>municipal-finance-project-design-manual-v1-0</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -12763,24 +13088,16 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FY 2018-19 Popular Annual Financial Report.pdf</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>FY18</t>
-        </is>
-      </c>
+          <t>Municipal Finance Project Design Manual v1.0.xlsx</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>20 pages</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>Machine-readable source</t>
@@ -12793,14 +13110,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>8beb9b82d9a9c15f…</t>
+          <t>1a917f31b130a274…</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>fy-26-27-cip-online-version</t>
+          <t>oc-hillsborough-fiscal-analysis-project</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -12810,24 +13127,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FY 26-27 CIP Online Version.pdf</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>FY26</t>
-        </is>
-      </c>
+          <t>OC &amp; Hillsborough Fiscal Analysis Project.docx</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>184 pages</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>Machine-readable source</t>
@@ -12840,14 +13149,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>9a788a792b641c01…</t>
+          <t>7ff6409f36a3503b…</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>fy2025-26-operating-budget-introduction</t>
+          <t>4-b-cip-presentation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -12857,14 +13166,10 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FY2025-26 Operating Budget Introduction.pdf</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>FY25</t>
-        </is>
-      </c>
+          <t>4-b - CIP Presentation.pdf</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Other</t>
@@ -12872,7 +13177,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>31 pages</t>
+          <t>22 pages</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -12887,14 +13192,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>bb7ec5fb47c0362b…</t>
+          <t>3dc0fef3cdf0c2a8…</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>fy2025-26-operating-budget-transmittal-letter</t>
+          <t>4-b-1-county-managers-cip-transmittal-letter-final</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -12904,14 +13209,10 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FY2025-26 Operating Budget Transmittal Letter.pdf</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>FY25</t>
-        </is>
-      </c>
+          <t>4-b 1 - County Managers CIP Transmittal Letter - FINAL.pdf</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>Other</t>
@@ -12919,7 +13220,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>17 pages</t>
+          <t>16 pages</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -12934,14 +13235,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0a9e59e868511cd4…</t>
+          <t>5f2158d47bc5d5a0…</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>fy2026-27-manager-s-recommended-budget</t>
+          <t>appendix-a-county-profile-data-element-pdf</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -12951,14 +13252,10 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>FY2026-27 Manager_s Recommended Budget.pdf</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>FY26</t>
-        </is>
-      </c>
+          <t>Appendix A_ County Profile (Data) Element (PDF).pdf</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>Other</t>
@@ -12966,7 +13263,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>352 pages</t>
+          <t>100 pages</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -12981,14 +13278,14 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>f2366d5e1da1315f…</t>
+          <t>1de901e83a325591…</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>fy2026-27-managers-recommended-budget</t>
+          <t>budget-ordinance-fy2025-26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -12998,12 +13295,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>FY2026-27 Managers Recommended Budget.pdf</t>
+          <t>Budget Ordinance FY2025-26.pdf</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>FY26</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -13013,7 +13310,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>357 pages</t>
+          <t>14 pages</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -13028,14 +13325,14 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>6d5892a97ae1d0b6…</t>
+          <t>5048fa9fae4e6313…</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>fy2026-27-operating-budget-introduction2</t>
+          <t>fy-2018-19-annual-financial-report</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -13045,12 +13342,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>FY2026-27 Operating Budget Introduction2.pdf</t>
+          <t>FY 2018-19 Annual Financial Report.pdf</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FY26</t>
+          <t>FY18</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -13060,7 +13357,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>34 pages</t>
+          <t>182 pages</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -13075,14 +13372,14 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>39e3cf008d9289e1…</t>
+          <t>606601997980895e…</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>fy202627-managers-messager</t>
+          <t>fy-2018-19-popular-annual-financial-report</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -13092,10 +13389,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FY202627 Managers MessageR.pdf</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>FY 2018-19 Popular Annual Financial Report.pdf</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>FY18</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>Other</t>
@@ -13103,7 +13404,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>12 pages</t>
+          <t>20 pages</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -13118,14 +13419,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>a7130e803d941c1a…</t>
+          <t>8beb9b82d9a9c15f…</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>fy25-26-approved-budget-web-version</t>
+          <t>fy-26-27-cip-online-version</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -13135,12 +13436,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>FY25-26 Approved Budget (Web Version).pdf</t>
+          <t>FY 26-27 CIP Online Version.pdf</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FY25</t>
+          <t>FY26</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -13150,7 +13451,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>508 pages</t>
+          <t>184 pages</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -13165,14 +13466,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>304d36fe692ed0b7…</t>
+          <t>9a788a792b641c01…</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>fy25-26-manager-recommended-budget</t>
+          <t>fy2025-26-operating-budget-introduction</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -13182,7 +13483,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>FY25-26 Manager Recommended Budget.pdf</t>
+          <t>FY2025-26 Operating Budget Introduction.pdf</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -13197,7 +13498,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>336 pages</t>
+          <t>31 pages</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -13212,14 +13513,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>ea0aa8476f0a4649…</t>
+          <t>bb7ec5fb47c0362b…</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>fy26-27-commissioner-approved-fee-schedule</t>
+          <t>fy2025-26-operating-budget-transmittal-letter</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -13229,12 +13530,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FY26-27 Commissioner Approved Fee Schedule.pdf</t>
+          <t>FY2025-26 Operating Budget Transmittal Letter.pdf</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>FY26</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -13244,7 +13545,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>95 pages</t>
+          <t>17 pages</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -13259,14 +13560,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>8bde817153248323…</t>
+          <t>0a9e59e868511cd4…</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>issues-log</t>
+          <t>fy2026-27-manager-s-recommended-budget</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -13276,16 +13577,24 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Issues Log.xlsx</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>FY2026-27 Manager_s Recommended Budget.pdf</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>FY26</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Issues</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>352 pages</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>Machine-readable source</t>
@@ -13298,14 +13607,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>e43269868eb341b3…</t>
+          <t>f2366d5e1da1315f…</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>mfas-architecture-notebook</t>
+          <t>fy2026-27-managers-recommended-budget</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -13315,16 +13624,24 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MFAS Architecture Notebook.docx</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>FY2026-27 Managers Recommended Budget.pdf</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>FY26</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>357 pages</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>Machine-readable source</t>
@@ -13337,14 +13654,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>545f29f4d95ffec5…</t>
+          <t>6d5892a97ae1d0b6…</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>mfas-architecture-notebook-2</t>
+          <t>fy2026-27-operating-budget-introduction2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -13354,10 +13671,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MFAS Architecture Notebook.pdf</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>FY2026-27 Operating Budget Introduction2.pdf</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>FY26</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>Other</t>
@@ -13365,7 +13686,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>18 pages</t>
+          <t>34 pages</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -13380,14 +13701,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>c2ad4c28ca659cc1…</t>
+          <t>39e3cf008d9289e1…</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>mfas-conceptual-architecture</t>
+          <t>fy202627-managers-messager</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -13397,7 +13718,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MFAS Conceptual Architecture.docx</t>
+          <t>FY202627 Managers MessageR.pdf</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -13406,7 +13727,11 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>12 pages</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>Machine-readable source</t>
@@ -13419,14 +13744,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>7fc6ceb2b9492b20…</t>
+          <t>a7130e803d941c1a…</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>mfas-conceptual-architecture-2</t>
+          <t>fy25-26-approved-budget-web-version</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -13436,10 +13761,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MFAS Conceptual Architecture.pdf</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>FY25-26 Approved Budget (Web Version).pdf</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>FY25</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>Other</t>
@@ -13447,7 +13776,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>19 pages</t>
+          <t>508 pages</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -13462,14 +13791,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>6071c5d487b22b70…</t>
+          <t>304d36fe692ed0b7…</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>municipal-finance-project-design-manual-v1-0</t>
+          <t>fy25-26-manager-recommended-budget</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -13479,16 +13808,24 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Municipal Finance Project Design Manual v1.0.xlsx</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>FY25-26 Manager Recommended Budget.pdf</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>FY25</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>336 pages</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
           <t>Machine-readable source</t>
@@ -13501,14 +13838,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1a917f31b130a274…</t>
+          <t>ea0aa8476f0a4649…</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>oc-design</t>
+          <t>fy26-27-commissioner-approved-fee-schedule</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -13518,16 +13855,24 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>OC Design.xlsx</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>FY26-27 Commissioner Approved Fee Schedule.pdf</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>FY26</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>95 pages</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
           <t>Machine-readable source</t>
@@ -13540,14 +13885,14 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>f66c9479c9ee9504…</t>
+          <t>8bde817153248323…</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>oc-pafr-2020</t>
+          <t>oc-design</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -13557,7 +13902,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>OC_PAFR_2020.pdf</t>
+          <t>OC Design.xlsx</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -13566,11 +13911,7 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>20 pages</t>
-        </is>
-      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>Machine-readable source</t>
@@ -13583,14 +13924,14 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>7f2bd6697b7d8550…</t>
+          <t>f66c9479c9ee9504…</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>orange-co-acfr-6-30-25final</t>
+          <t>oc-pafr-2020</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13600,7 +13941,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Orange Co ACFR 6.30.25Final.pdf</t>
+          <t>OC_PAFR_2020.pdf</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -13611,7 +13952,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>231 pages</t>
+          <t>20 pages</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -13626,14 +13967,14 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>e962e7674ecad847…</t>
+          <t>7f2bd6697b7d8550…</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>orange-co-acfr-6-30-24-final</t>
+          <t>orange-co-acfr-6-30-25final</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13643,7 +13984,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Orange Co ACFR 6_30_24 Final_.pdf</t>
+          <t>Orange Co ACFR 6.30.25Final.pdf</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -13654,7 +13995,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>227 pages</t>
+          <t>231 pages</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -13669,14 +14010,14 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>cfb25d100dfe45b4…</t>
+          <t>e962e7674ecad847…</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>orange-county-2018-cafr</t>
+          <t>orange-co-acfr-6-30-24-final</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -13686,7 +14027,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Orange County 2018 CAFR.pdf</t>
+          <t>Orange Co ACFR 6_30_24 Final_.pdf</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -13697,7 +14038,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>173 pages</t>
+          <t>227 pages</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -13712,14 +14053,14 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1146f1d25c6ea129…</t>
+          <t>cfb25d100dfe45b4…</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>orange-county-6-30-21-acfr-client-1</t>
+          <t>orange-county-2018-cafr</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -13729,7 +14070,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Orange County 6-30-21 ACFR - client_1.pdf</t>
+          <t>Orange County 2018 CAFR.pdf</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -13740,7 +14081,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>189 pages</t>
+          <t>173 pages</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -13755,14 +14096,14 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0793cd4978c0dab7…</t>
+          <t>1146f1d25c6ea129…</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>orange-county-6-30-21-compliance-report-client</t>
+          <t>orange-county-6-30-21-acfr-client-1</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -13772,7 +14113,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Orange County 6-30-21 Compliance Report - client.pdf</t>
+          <t>Orange County 6-30-21 ACFR - client_1.pdf</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -13783,7 +14124,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>30 pages</t>
+          <t>189 pages</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -13798,14 +14139,14 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>6b4b31542848aa8d…</t>
+          <t>0793cd4978c0dab7…</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>orange-county-acfr-6-30-22-final-2</t>
+          <t>orange-county-6-30-21-compliance-report-client</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -13815,7 +14156,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Orange County ACFR 6.30.22 Final_2.pdf</t>
+          <t>Orange County 6-30-21 Compliance Report - client.pdf</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -13826,7 +14167,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>226 pages</t>
+          <t>30 pages</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -13841,14 +14182,14 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>f2bafc61c0929216…</t>
+          <t>6b4b31542848aa8d…</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>orange-county-cafr-6-30-20</t>
+          <t>orange-county-acfr-6-30-22-final-2</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -13858,7 +14199,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Orange County CAFR 6.30.20.pdf</t>
+          <t>Orange County ACFR 6.30.22 Final_2.pdf</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -13869,7 +14210,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>181 pages</t>
+          <t>226 pages</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -13884,14 +14225,14 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>e41a2c234f9d9a19…</t>
+          <t>f2bafc61c0929216…</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>orange-county-nc-acfr-6-30-23</t>
+          <t>orange-county-cafr-6-30-20</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -13901,7 +14242,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Orange County NC ACFR 6.30.23.pdf</t>
+          <t>Orange County CAFR 6.30.20.pdf</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -13912,7 +14253,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>227 pages</t>
+          <t>181 pages</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -13927,14 +14268,14 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>de96f5845a9ddc7a…</t>
+          <t>e41a2c234f9d9a19…</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>orange-county-municipal-finance-database-v1-0</t>
+          <t>orange-county-nc-acfr-6-30-23</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -13944,7 +14285,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Orange_County_Municipal_Finance_Database_v1.0.xlsx</t>
+          <t>Orange County NC ACFR 6.30.23.pdf</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -13953,7 +14294,11 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>227 pages</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>Machine-readable source</t>
@@ -13966,14 +14311,14 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>d819f7eab876f57d…</t>
+          <t>de96f5845a9ddc7a…</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>orange-county-municipal-finance-database-v1-1</t>
+          <t>orange-county-municipal-finance-database-v1-0</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -13983,7 +14328,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Orange_County_Municipal_Finance_Database_v1.1.xlsx</t>
+          <t>Orange_County_Municipal_Finance_Database_v1.0.xlsx</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -14005,14 +14350,14 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>359a2e63e4d0faea…</t>
+          <t>d819f7eab876f57d…</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>orange-county-municipal-financial-data-warehouse-v1-2</t>
+          <t>orange-county-municipal-finance-database-v1-1</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -14022,7 +14367,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Orange_County_Municipal_Financial_Data_Warehouse_v1.2.xlsx</t>
+          <t>Orange_County_Municipal_Finance_Database_v1.1.xlsx</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -14044,14 +14389,14 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>8ca50c7d1d9b59ae…</t>
+          <t>359a2e63e4d0faea…</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>orange-county-municipal-financial-data-warehouse-v2-0</t>
+          <t>orange-county-municipal-financial-data-warehouse-v1-2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -14061,7 +14406,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Orange_County_Municipal_Financial_Data_Warehouse_v2.0.xlsx</t>
+          <t>Orange_County_Municipal_Financial_Data_Warehouse_v1.2.xlsx</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -14083,14 +14428,14 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>d1c0019c2745468a…</t>
+          <t>8ca50c7d1d9b59ae…</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>orange-county-municipal-financial-information-system-v2-2-foundation</t>
+          <t>orange-county-municipal-financial-data-warehouse-v2-0</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -14100,7 +14445,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Orange_County_Municipal_Financial_Information_System_v2.2_Foundation.xlsx</t>
+          <t>Orange_County_Municipal_Financial_Data_Warehouse_v2.0.xlsx</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -14122,14 +14467,14 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>600ff180a3e058b3…</t>
+          <t>d1c0019c2745468a…</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>redatarequestlongtermfiscaltrendandsustainability</t>
+          <t>orange-county-municipal-financial-information-system-v2-2-foundation</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -14139,13 +14484,13 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>redatarequestlongtermfiscaltrendandsustainability.zip</t>
+          <t>Orange_County_Municipal_Financial_Information_System_v2.2_Foundation.xlsx</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Financial-Report</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
@@ -14161,7 +14506,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>c7b6ae4934174283…</t>
+          <t>600ff180a3e058b3…</t>
         </is>
       </c>
     </row>
@@ -15787,7 +16132,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>oc-hillsborough-fiscal-analysis-project</t>
+          <t>organizational-chart-of-town-services-and-administration-20230106</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -15797,16 +16142,20 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>OC &amp; Hillsborough Fiscal Analysis Project.docx</t>
+          <t>Organizational Chart of Town Services and Administration 20230106.pdf</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr"/>
+          <t>Budget</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>1 pages</t>
+        </is>
+      </c>
       <c r="G81" t="inlineStr">
         <is>
           <t>Machine-readable source</t>
@@ -15819,14 +16168,14 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>7ff6409f36a3503b…</t>
+          <t>0ea1fa2f88125d04…</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>organizational-chart-of-town-services-and-administration-20230106</t>
+          <t>recommended-fy27budgetataglanceflyer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -15836,7 +16185,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Organizational Chart of Town Services and Administration 20230106.pdf</t>
+          <t>Recommended FY27BudgetAtAGlanceFlyer.pdf</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -15862,14 +16211,14 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>0ea1fa2f88125d04…</t>
+          <t>b1aef110d4229f1d…</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>recommended-fy27budgetataglanceflyer</t>
+          <t>sales-tax-information</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -15879,20 +16228,16 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Recommended FY27BudgetAtAGlanceFlyer.pdf</t>
+          <t>Sales Tax Information.docx</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Budget</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>1 pages</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
           <t>Machine-readable source</t>
@@ -15905,14 +16250,14 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>b1aef110d4229f1d…</t>
+          <t>60ec376a43d36307…</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>sales-tax-information</t>
+          <t>stormwater-presentation-202404</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -15922,16 +16267,20 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Sales Tax Information.docx</t>
+          <t>Stormwater Presentation 202404.pdf</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr"/>
+          <t>Budget</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>14 pages</t>
+        </is>
+      </c>
       <c r="G84" t="inlineStr">
         <is>
           <t>Machine-readable source</t>
@@ -15944,14 +16293,14 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>60ec376a43d36307…</t>
+          <t>816c7eaa0623fddd…</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>stormwater-presentation-202404</t>
+          <t>water-and-sewer-utility-rate-study-20240531</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -15961,7 +16310,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Stormwater Presentation 202404.pdf</t>
+          <t>Water and Sewer Utility Rate Study 20240531.pdf</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -15972,7 +16321,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>14 pages</t>
+          <t>27 pages</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -15987,14 +16336,14 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>816c7eaa0623fddd…</t>
+          <t>d113a20dca03f82e…</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>water-and-sewer-utility-rate-study-20240531</t>
+          <t>redatarequestlongtermfiscaltrendandsustainability</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -16004,20 +16353,16 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Water and Sewer Utility Rate Study 20240531.pdf</t>
+          <t>redatarequestlongtermfiscaltrendandsustainability.zip</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Budget</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>27 pages</t>
-        </is>
-      </c>
+          <t>Financial-Report</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
           <t>Machine-readable source</t>
@@ -16030,7 +16375,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>d113a20dca03f82e…</t>
+          <t>c7b6ae4934174283…</t>
         </is>
       </c>
     </row>

--- a/data/exports/MFAS_Data_Warehouse.xlsx
+++ b/data/exports/MFAS_Data_Warehouse.xlsx
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
@@ -9458,7 +9458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9888,7 +9888,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q019</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -9898,29 +9898,29 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Wording — where figures come from</t>
+          <t>Revenue by source</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>The original sentence was not quite true and a sceptical reader could catch it: 31 of the 84 documents concern Orange County rather than the town, and 14 of the 83 published figures come from the initiative's own request workbook — the administrative-spend series a commissioner supplied, and two capital-project cost changes. Each of those is already labelled where it appears. (The masthead was not the only place: the page's meta description carried the same claim and was corrected separately.) Changed rather than left, because the strongest sentence on the page is the worst one to have to walk back.</t>
+          <t>Her words: "The broader view includes revenue from sources such as Grants, State, Other Funds, etc. So I want to make sure we have this broader view too."</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Your decision</t>
+          <t>Work this project owes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Q017</t>
+          <t>Q020</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -9930,29 +9930,29 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Resident film</t>
+          <t>Stacked waterfall</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>It only appeared in the README before, where no resident will ever look. Placed as an offer on the judgement that a reader who arrives annoyed about a tax bill wants their own number first — but it is your film and the call is yours.</t>
+          <t>Her stated preference for the visual, and her own Workbook B opens with a Budget Waterfall sheet.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Your decision</t>
+          <t>Work this project owes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Q018</t>
+          <t>Q021</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -9962,7 +9962,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Resident film</t>
+          <t>Total cost of ownership</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -9970,21 +9970,17 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>The sentence was superseded because the site now publishes the audited record recovered from those scans. Since this was first raised, a second audit widened it: the narration itself says at ~49s that "Every figure names the document and the page it came from", which overpromises the same way the old masthead did (14 figures come from spreadsheet cells that have no page); and the film's "2 governments / 6 documents / 1,031 pages" hold shows counts that changed when the archive's duplicate county budget stopped being counted twice (now 5 documents, 679 pages — the masthead card was switched to the film's opening question so the stale figures no longer sit on the front page, but they remain inside the film). Re-cutting means regenerating machine narration and music, so it is a cost and an ownership question rather than a fix this project should make unasked.</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Your decision</t>
+          <t>Work this project owes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Q019</t>
+          <t>Q022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -9994,71 +9990,71 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Revenue by source</t>
+          <t>README film links if the repo moves</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Her words: "The broader view includes revenue from sources such as Grants, State, Other Funds, etc. So I want to make sure we have this broader view too."</t>
+          <t>They cannot be repo-relative: GitHub's blob viewer refuses the file outright ("we can't show files that are this big right now") and raw.githubusercontent serves it as application/octet-stream, which downloads instead of playing. Only Pages serves it as video/mp4 with Accept-Ranges. Measured, not assumed.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Work this project owes</t>
+          <t>Your decision</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Q020</t>
+          <t>Q027</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Stacked waterfall</t>
+          <t>Driver: Salary and benefit increases</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Her stated preference for the visual, and her own Workbook B opens with a Budget Waterfall sheet.</t>
+          <t>Her own follow-up against a $630,000 driver</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Work this project owes</t>
+          <t>Records request to the Town</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Q021</t>
+          <t>Q028</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Total cost of ownership</t>
+          <t>Driver: FY26 market pay adjustments</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -10066,27 +10062,31 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Her own follow-up against a $220,000 driver</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Work this project owes</t>
+          <t>Records request to the Town</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Q022</t>
+          <t>Q029</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>README film links if the repo moves</t>
+          <t>Driver: Fire station reserve / future debt gap</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -10096,19 +10096,19 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>They cannot be repo-relative: GitHub's blob viewer refuses the file outright ("we can't show files that are this big right now") and raw.githubusercontent serves it as application/octet-stream, which downloads instead of playing. Only Pages serves it as video/mp4 with Accept-Ranges. Measured, not assumed.</t>
+          <t>Her own follow-up against a $370,000 driver</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Your decision</t>
+          <t>Records request to the Town</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Q027</t>
+          <t>Q030</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Driver: Salary and benefit increases</t>
+          <t>Driver: Ridgewalk Greenway reserve / future debt gap</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -10128,7 +10128,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Her own follow-up against a $630,000 driver</t>
+          <t>Her own follow-up against a $337,000 driver</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -10140,7 +10140,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Q028</t>
+          <t>Q031</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -10150,7 +10150,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Driver: FY26 market pay adjustments</t>
+          <t>Driver: Passenger rail / multi-modal station town share</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -10160,7 +10160,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Her own follow-up against a $220,000 driver</t>
+          <t>Her own follow-up against a $3,500,000 driver</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -10172,7 +10172,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Q029</t>
+          <t>Q032</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10182,7 +10182,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Driver: Fire station reserve / future debt gap</t>
+          <t>Driver: Affordable housing annual contribution target</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -10192,7 +10192,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Her own follow-up against a $370,000 driver</t>
+          <t>Her own follow-up against a $320,000 driver</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -10204,7 +10204,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q033</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10214,7 +10214,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Driver: Ridgewalk Greenway reserve / future debt gap</t>
+          <t>Driver: FY26 affordable housing major expense</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -10224,7 +10224,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Her own follow-up against a $337,000 driver</t>
+          <t>Her own follow-up against a $376,000 driver</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -10236,7 +10236,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Q031</t>
+          <t>Q034</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Driver: Passenger rail / multi-modal station town share</t>
+          <t>Driver: Nonprofit partnership funding growth</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Her own follow-up against a $3,500,000 driver</t>
+          <t>Her own follow-up against a $110,000 driver</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -10268,7 +10268,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Q032</t>
+          <t>Q035</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -10278,7 +10278,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Driver: Affordable housing annual contribution target</t>
+          <t>Driver: Public Space and Sustainability annual commitment</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -10300,7 +10300,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Q033</t>
+          <t>Q036</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -10310,7 +10310,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Driver: FY26 affordable housing major expense</t>
+          <t>Driver: Community Services reorganization</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Her own follow-up against a $376,000 driver</t>
+          <t>Her own follow-up against a $60,423 driver</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -10332,7 +10332,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Q034</t>
+          <t>Q037</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -10342,7 +10342,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Driver: Nonprofit partnership funding growth</t>
+          <t>Driver: Police cameras and equipment</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -10352,7 +10352,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Her own follow-up against a $110,000 driver</t>
+          <t>Her own follow-up against a $75,000 driver</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -10364,7 +10364,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Q035</t>
+          <t>Q038</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Driver: Public Space and Sustainability annual commitment</t>
+          <t>Driver: Vehicle replacement funds</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -10384,7 +10384,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Her own follow-up against a $320,000 driver</t>
+          <t>Her own follow-up against a $300,000 driver</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -10396,7 +10396,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Q036</t>
+          <t>Q039</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Driver: Community Services reorganization</t>
+          <t>Driver: Sales tax flatline</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -10414,11 +10414,7 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Her own follow-up against a $60,423 driver</t>
-        </is>
-      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>Records request to the Town</t>
@@ -10428,7 +10424,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Q037</t>
+          <t>Q040</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -10438,7 +10434,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Driver: Police cameras and equipment</t>
+          <t>Driver: Projected FY29 deficit</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -10448,7 +10444,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Her own follow-up against a $75,000 driver</t>
+          <t>Her own follow-up against a $-2,534,674 driver</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -10460,17 +10456,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Q038</t>
+          <t>Q041</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Driver: Vehicle replacement funds</t>
+          <t>County workbook — Source_Register alignment</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -10480,19 +10476,19 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Her own follow-up against a $300,000 driver</t>
+          <t>The county table's figures are yours and are published as yours, but only FY2018's row can currently be re-verified against a held report. Aligning the register makes every year checkable the way FY2018 already is.</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Records request to the Town</t>
+          <t>Your decision</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Q039</t>
+          <t>Q042</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -10502,7 +10498,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Driver: Sales tax flatline</t>
+          <t>Dam Repairs — funding vs expenditure totals</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -10510,7 +10506,11 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Both tables are printed in the same document and both add up internally, so this is a question about the document rather than an extraction error — exactly the kind of difference a resident checking the numbers would find.</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr">
         <is>
           <t>Records request to the Town</t>
@@ -10520,17 +10520,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Q040</t>
+          <t>Q043</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Driver: Projected FY29 deficit</t>
+          <t>Question-register id stability</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -10540,19 +10540,19 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Her own follow-up against a $-2,534,674 driver</t>
+          <t>Amy asked for this register specifically to track her open questions; an id that silently changes meaning defeats that. Append-only is the interim rule as of this audit, but it relies on discipline rather than the generator.</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Records request to the Town</t>
+          <t>Repository owner action</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Q041</t>
+          <t>Q044</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -10562,7 +10562,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>County workbook — Source_Register alignment</t>
+          <t>Wording — who adopts the budget</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -10572,7 +10572,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>The county table's figures are yours and are published as yours, but only FY2018's row can currently be re-verified against a held report. Aligning the register makes every year checkable the way FY2018 already is.</t>
+          <t>A claim about who exercises a power is the kind a resident can check against the town charter, and the archive cannot settle it either way — so it is flagged rather than silently rewritten.</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -10584,17 +10584,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Q042</t>
+          <t>Q045</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dam Repairs — funding vs expenditure totals</t>
+          <t>Stormwater Fund reconciliation checks</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -10604,106 +10604,10 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Both tables are printed in the same document and both add up internally, so this is a question about the document rather than an extraction error — exactly the kind of difference a resident checking the numbers would find.</t>
+          <t>A fund with no checks is indistinguishable on screen from a fund that failed them. The explorer now says so explicitly, but the honest fix is to run the checks.</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
-        <is>
-          <t>Records request to the Town</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Q043</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Question-register id stability</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Amy asked for this register specifically to track her open questions; an id that silently changes meaning defeats that. Append-only is the interim rule as of this audit, but it relies on discipline rather than the generator.</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Repository owner action</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Q044</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Wording — who adopts the budget</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>A claim about who exercises a power is the kind a resident can check against the town charter, and the archive cannot settle it either way — so it is flagged rather than silently rewritten.</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Your decision</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Q045</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Stormwater Fund reconciliation checks</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>A fund with no checks is indistinguishable on screen from a fund that failed them. The explorer now says so explicitly, but the honest fix is to run the checks.</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
         <is>
           <t>Work this project owes</t>
         </is>
@@ -11385,12 +11289,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>answered</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>The original sentence was not quite true and a sceptical reader could catch it: 31 of the 84 documents concern Orange County rather than the town, and 14 of the 83 published figures come from the initiative's own request workbook — the administrative-spend series a commissioner supplied, and two capital-project cost changes. Each of those is already labelled where it appears. (The masthead was not the only place: the page's meta description carried the same claim and was corrected separately.) Changed rather than left, because the strongest sentence on the page is the worst one to have to walk back.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>David settled it on 2026-07-29: the corrected wording stands and is live. Kept here because it is a change to the most prominent sentence on the site and to how the project describes its own sourcing — if you would put it differently, say so and it changes. Nothing about it is expensive to revisit.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -11422,12 +11331,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>answered</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>It only appeared in the README before, where no resident will ever look. Placed as an offer on the judgement that a reader who arrives annoyed about a tax bill wants their own number first — but it is your film and the call is yours.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>David settled it on 2026-07-29: it stays an offer. The reader reaches the calculator, or a button pointing at it, before the film in every layout, and nothing of the film downloads until somebody presses play.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -11459,12 +11373,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>answered</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>The sentence was superseded because the site now publishes the audited record recovered from those scans. Since this was first raised, a second audit widened it: the narration itself says at ~49s that "Every figure names the document and the page it came from", which overpromises the same way the old masthead did (14 figures come from spreadsheet cells that have no page); and the film's "2 governments / 6 documents / 1,031 pages" hold shows counts that changed when the archive's duplicate county budget stopped being counted twice (now 5 documents, 679 pages — the masthead card was switched to the film's opening question so the stale figures no longer sit on the front page, but they remain inside the film). Re-cutting means regenerating machine narration and music, so it is a cost and an ownership question rather than a fix this project should make unasked.</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>David settled it on 2026-07-29: no re-cut, the film stays exactly as it was cut. That leaves two claims inside it that the data has since moved past, so they are now corrected in writing beside the film on the site itself — the 6 documents / 1,031 pages hold against the checked 5 and 679, and the closing promise of a page for every figure against the 14 that come from spreadsheet cells. The correction is computed from the data rather than typed in, so it will disappear by itself if the film is ever re-cut to match. Reporting our own source's errors instead of quietly living with them is the same rule this project applies to the county's misprinted tax-rate table.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">

--- a/data/exports/MFAS_Data_Warehouse.xlsx
+++ b/data/exports/MFAS_Data_Warehouse.xlsx
@@ -11383,7 +11383,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>David settled it on 2026-07-29: no re-cut, the film stays exactly as it was cut. That leaves two claims inside it that the data has since moved past, so they are now corrected in writing beside the film on the site itself — the 6 documents / 1,031 pages hold against the checked 5 and 679, and the closing promise of a page for every figure against the 14 that come from spreadsheet cells. The correction is computed from the data rather than typed in, so it will disappear by itself if the film is ever re-cut to match. Reporting our own source's errors instead of quietly living with them is the same rule this project applies to the county's misprinted tax-rate table.</t>
+          <t>David settled it on 2026-07-29, and the reasoning is worth keeping: a film is a snapshot of the day it was cut, not a view onto live data. The archive will keep moving — documents get deduplicated, figures get re-checked — and the film cannot be re-recorded every time it does, so the sensible thing is to let it be a film. It is left exactly as cut, and no correction is carried on the page beside it either: the site's own figures are the ones that must be right and are checked on every build, and annotating a 62-second introduction with the archive's revision history would tell a resident nothing they came for. Anyone reading a figure off the film and wanting to rely on it will find the current one, sourced, on the page it is advertising.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
